--- a/research/traditional_assets/database/data/malawi/malawi_food_processing.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_food_processing.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1464918932168536</v>
+        <v>0.1463859013236367</v>
       </c>
       <c r="C2">
-        <v>561.7923608197423</v>
+        <v>556.7836467256642</v>
       </c>
       <c r="D2">
-        <v>561.7923608197423</v>
+        <v>562.3843467256642</v>
       </c>
       <c r="E2">
-        <v>-2.27</v>
+        <v>3.3307</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.6007</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1451,28 +1451,28 @@
         <v>48.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.28171521</v>
       </c>
       <c r="N2">
-        <v>48.3</v>
+        <v>48.01828479</v>
       </c>
       <c r="O2">
-        <v>4.83</v>
+        <v>4.801828479</v>
       </c>
       <c r="P2">
-        <v>43.47</v>
+        <v>43.21645631099999</v>
       </c>
       <c r="Q2">
-        <v>53.17</v>
+        <v>52.916456311</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1464918932168536</v>
+        <v>0.1474072740642795</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6214174396239315</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>171.4497417445086</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1463859013236367</v>
+        <v>0.1462799094304199</v>
       </c>
       <c r="C3">
-        <v>556.7836467256642</v>
+        <v>551.7761815520379</v>
       </c>
       <c r="D3">
-        <v>562.3843467256642</v>
+        <v>562.9775815520379</v>
       </c>
       <c r="E3">
-        <v>3.3307</v>
+        <v>8.9314</v>
       </c>
       <c r="F3">
-        <v>5.6007</v>
+        <v>11.2014</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1533,28 +1533,28 @@
         <v>48.3</v>
       </c>
       <c r="M3">
-        <v>0.28171521</v>
+        <v>0.56343042</v>
       </c>
       <c r="N3">
-        <v>48.01828479</v>
+        <v>47.73656957999999</v>
       </c>
       <c r="O3">
-        <v>4.801828479</v>
+        <v>4.773656957999999</v>
       </c>
       <c r="P3">
-        <v>43.21645631099999</v>
+        <v>42.962912622</v>
       </c>
       <c r="Q3">
-        <v>52.916456311</v>
+        <v>52.662912622</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1474072740642795</v>
+        <v>0.1483413361534897</v>
       </c>
       <c r="T3">
-        <v>0.6214174396239315</v>
+        <v>0.6271300470850818</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>171.4497417445086</v>
+        <v>85.72487087225429</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1462799094304199</v>
+        <v>0.146173917537203</v>
       </c>
       <c r="C4">
-        <v>551.7761815520379</v>
+        <v>546.7699692553319</v>
       </c>
       <c r="D4">
-        <v>562.9775815520379</v>
+        <v>563.5720692553319</v>
       </c>
       <c r="E4">
-        <v>8.9314</v>
+        <v>14.5321</v>
       </c>
       <c r="F4">
-        <v>11.2014</v>
+        <v>16.8021</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1615,28 +1615,28 @@
         <v>48.3</v>
       </c>
       <c r="M4">
-        <v>0.56343042</v>
+        <v>0.8451456299999998</v>
       </c>
       <c r="N4">
-        <v>47.73656957999999</v>
+        <v>47.45485437</v>
       </c>
       <c r="O4">
-        <v>4.773656957999999</v>
+        <v>4.745485437</v>
       </c>
       <c r="P4">
-        <v>42.962912622</v>
+        <v>42.709368933</v>
       </c>
       <c r="Q4">
-        <v>52.662912622</v>
+        <v>52.409368933</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1483413361534897</v>
+        <v>0.1492946572548485</v>
       </c>
       <c r="T4">
-        <v>0.6271300470850818</v>
+        <v>0.6329604402670805</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>85.72487087225429</v>
+        <v>57.1499139148362</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.146173917537203</v>
+        <v>0.1460679256439862</v>
       </c>
       <c r="C5">
-        <v>546.7699692553319</v>
+        <v>541.7650138087461</v>
       </c>
       <c r="D5">
-        <v>563.5720692553319</v>
+        <v>564.167813808746</v>
       </c>
       <c r="E5">
-        <v>14.5321</v>
+        <v>20.1328</v>
       </c>
       <c r="F5">
-        <v>16.8021</v>
+        <v>22.4028</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1697,28 +1697,28 @@
         <v>48.3</v>
       </c>
       <c r="M5">
-        <v>0.8451456299999998</v>
+        <v>1.12686084</v>
       </c>
       <c r="N5">
-        <v>47.45485437</v>
+        <v>47.17313916</v>
       </c>
       <c r="O5">
-        <v>4.745485437</v>
+        <v>4.717313916</v>
       </c>
       <c r="P5">
-        <v>42.709368933</v>
+        <v>42.455825244</v>
       </c>
       <c r="Q5">
-        <v>52.409368933</v>
+        <v>52.155825244</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1492946572548485</v>
+        <v>0.1502678392124856</v>
       </c>
       <c r="T5">
-        <v>0.6329604402670805</v>
+        <v>0.6389122999737044</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.1499139148362</v>
+        <v>42.86243543612714</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1460679256439862</v>
+        <v>0.1459619337507693</v>
       </c>
       <c r="C6">
-        <v>541.7650138087461</v>
+        <v>536.761319202296</v>
       </c>
       <c r="D6">
-        <v>564.167813808746</v>
+        <v>564.7648192022961</v>
       </c>
       <c r="E6">
-        <v>20.1328</v>
+        <v>25.7335</v>
       </c>
       <c r="F6">
-        <v>22.4028</v>
+        <v>28.0035</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1779,28 +1779,28 @@
         <v>48.3</v>
       </c>
       <c r="M6">
-        <v>1.12686084</v>
+        <v>1.40857605</v>
       </c>
       <c r="N6">
-        <v>47.17313916</v>
+        <v>46.89142395</v>
       </c>
       <c r="O6">
-        <v>4.717313916</v>
+        <v>4.689142395</v>
       </c>
       <c r="P6">
-        <v>42.455825244</v>
+        <v>42.202281555</v>
       </c>
       <c r="Q6">
-        <v>52.155825244</v>
+        <v>51.902281555</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1502678392124856</v>
+        <v>0.1512615092113361</v>
       </c>
       <c r="T6">
-        <v>0.6389122999737044</v>
+        <v>0.6449894619899411</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.86243543612714</v>
+        <v>34.28994834890171</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1459619337507693</v>
+        <v>0.1458559418575525</v>
       </c>
       <c r="C7">
-        <v>536.761319202296</v>
+        <v>531.7588894429053</v>
       </c>
       <c r="D7">
-        <v>564.7648192022961</v>
+        <v>565.3630894429053</v>
       </c>
       <c r="E7">
-        <v>25.7335</v>
+        <v>31.3342</v>
       </c>
       <c r="F7">
-        <v>28.0035</v>
+        <v>33.6042</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1861,28 +1861,28 @@
         <v>48.3</v>
       </c>
       <c r="M7">
-        <v>1.40857605</v>
+        <v>1.69029126</v>
       </c>
       <c r="N7">
-        <v>46.89142395</v>
+        <v>46.60970873999999</v>
       </c>
       <c r="O7">
-        <v>4.689142395</v>
+        <v>4.660970873999999</v>
       </c>
       <c r="P7">
-        <v>42.202281555</v>
+        <v>41.94873786599999</v>
       </c>
       <c r="Q7">
-        <v>51.902281555</v>
+        <v>51.648737866</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1512615092113361</v>
+        <v>0.1522763211250558</v>
       </c>
       <c r="T7">
-        <v>0.6449894619899411</v>
+        <v>0.6511959253256725</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.28994834890171</v>
+        <v>28.5749569574181</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1458559418575525</v>
+        <v>0.1457499499643356</v>
       </c>
       <c r="C8">
-        <v>531.7588894429053</v>
+        <v>526.7577285544944</v>
       </c>
       <c r="D8">
-        <v>565.3630894429053</v>
+        <v>565.9626285544944</v>
       </c>
       <c r="E8">
-        <v>31.33419999999999</v>
+        <v>36.93489999999999</v>
       </c>
       <c r="F8">
-        <v>33.60419999999999</v>
+        <v>39.20489999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1943,28 +1943,28 @@
         <v>48.3</v>
       </c>
       <c r="M8">
-        <v>1.69029126</v>
+        <v>1.97200647</v>
       </c>
       <c r="N8">
-        <v>46.60970873999999</v>
+        <v>46.32799353</v>
       </c>
       <c r="O8">
-        <v>4.660970873999999</v>
+        <v>4.632799353</v>
       </c>
       <c r="P8">
-        <v>41.94873786599999</v>
+        <v>41.695194177</v>
       </c>
       <c r="Q8">
-        <v>51.648737866</v>
+        <v>51.395194177</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1522763211250558</v>
+        <v>0.1533129569508985</v>
       </c>
       <c r="T8">
-        <v>0.6511959253256725</v>
+        <v>0.6575358609912044</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.5749569574181</v>
+        <v>24.49282024921552</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1457499499643356</v>
+        <v>0.1456439580711188</v>
       </c>
       <c r="C9">
-        <v>526.7577285544942</v>
+        <v>521.7578405780696</v>
       </c>
       <c r="D9">
-        <v>565.9626285544941</v>
+        <v>566.5634405780696</v>
       </c>
       <c r="E9">
-        <v>36.9349</v>
+        <v>42.5356</v>
       </c>
       <c r="F9">
-        <v>39.2049</v>
+        <v>44.8056</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2025,28 +2025,28 @@
         <v>48.3</v>
       </c>
       <c r="M9">
-        <v>1.97200647</v>
+        <v>2.25372168</v>
       </c>
       <c r="N9">
-        <v>46.32799353</v>
+        <v>46.04627832</v>
       </c>
       <c r="O9">
-        <v>4.632799353</v>
+        <v>4.604627832</v>
       </c>
       <c r="P9">
-        <v>41.695194177</v>
+        <v>41.441650488</v>
       </c>
       <c r="Q9">
-        <v>51.395194177</v>
+        <v>51.141650488</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1533129569508985</v>
+        <v>0.1543721283381726</v>
       </c>
       <c r="T9">
-        <v>0.6575358609912045</v>
+        <v>0.6640136213451175</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.49282024921551</v>
+        <v>21.43121771806357</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1456439580711188</v>
+        <v>0.1455379661779019</v>
       </c>
       <c r="C10">
-        <v>521.7578405780696</v>
+        <v>516.7592295718156</v>
       </c>
       <c r="D10">
-        <v>566.5634405780696</v>
+        <v>567.1655295718156</v>
       </c>
       <c r="E10">
-        <v>42.5356</v>
+        <v>48.13629999999999</v>
       </c>
       <c r="F10">
-        <v>44.8056</v>
+        <v>50.40629999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>48.3</v>
       </c>
       <c r="M10">
-        <v>2.25372168</v>
+        <v>2.53543689</v>
       </c>
       <c r="N10">
-        <v>46.04627832</v>
+        <v>45.76456311</v>
       </c>
       <c r="O10">
-        <v>4.604627832</v>
+        <v>4.576456311</v>
       </c>
       <c r="P10">
-        <v>41.441650488</v>
+        <v>41.188106799</v>
       </c>
       <c r="Q10">
-        <v>51.141650488</v>
+        <v>50.888106799</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1543721283381726</v>
+        <v>0.1554545782174746</v>
       </c>
       <c r="T10">
-        <v>0.6640136213451175</v>
+        <v>0.6706337500584573</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.43121771806357</v>
+        <v>19.0499713049454</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1455379661779019</v>
+        <v>0.1454319742846851</v>
       </c>
       <c r="C11">
-        <v>516.7592295718156</v>
+        <v>511.7618996111855</v>
       </c>
       <c r="D11">
-        <v>567.1655295718156</v>
+        <v>567.7688996111855</v>
       </c>
       <c r="E11">
-        <v>48.13629999999999</v>
+        <v>53.73699999999999</v>
       </c>
       <c r="F11">
-        <v>50.40629999999999</v>
+        <v>56.00699999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2189,28 +2189,28 @@
         <v>48.3</v>
       </c>
       <c r="M11">
-        <v>2.53543689</v>
+        <v>2.817152099999999</v>
       </c>
       <c r="N11">
-        <v>45.76456311</v>
+        <v>45.4828479</v>
       </c>
       <c r="O11">
-        <v>4.576456311</v>
+        <v>4.548284789999999</v>
       </c>
       <c r="P11">
-        <v>41.188106799</v>
+        <v>40.93456311</v>
       </c>
       <c r="Q11">
-        <v>50.888106799</v>
+        <v>50.63456311</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1554545782174746</v>
+        <v>0.156561082538539</v>
       </c>
       <c r="T11">
-        <v>0.6706337500584573</v>
+        <v>0.6774009927432046</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.0499713049454</v>
+        <v>17.14497417445086</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1454319742846851</v>
+        <v>0.1453259823914682</v>
       </c>
       <c r="C12">
-        <v>511.7618996111855</v>
+        <v>506.7658547889937</v>
       </c>
       <c r="D12">
-        <v>567.7688996111855</v>
+        <v>568.3735547889937</v>
       </c>
       <c r="E12">
-        <v>53.73699999999999</v>
+        <v>59.33769999999999</v>
       </c>
       <c r="F12">
-        <v>56.007</v>
+        <v>61.60769999999999</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2271,28 +2271,28 @@
         <v>48.3</v>
       </c>
       <c r="M12">
-        <v>2.8171521</v>
+        <v>3.09886731</v>
       </c>
       <c r="N12">
-        <v>45.4828479</v>
+        <v>45.20113268999999</v>
       </c>
       <c r="O12">
-        <v>4.548284789999999</v>
+        <v>4.520113268999999</v>
       </c>
       <c r="P12">
-        <v>40.93456311</v>
+        <v>40.68101942099999</v>
       </c>
       <c r="Q12">
-        <v>50.63456311</v>
+        <v>50.381019421</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.156561082538539</v>
+        <v>0.1576924521252452</v>
       </c>
       <c r="T12">
-        <v>0.6774009927432046</v>
+        <v>0.684320308297272</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.14497417445086</v>
+        <v>15.58634015859169</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1453259823914682</v>
+        <v>0.1452199904982514</v>
       </c>
       <c r="C13">
-        <v>506.7658547889937</v>
+        <v>501.7710992155074</v>
       </c>
       <c r="D13">
-        <v>568.3735547889937</v>
+        <v>568.9794992155074</v>
       </c>
       <c r="E13">
-        <v>59.33769999999999</v>
+        <v>64.93839999999999</v>
       </c>
       <c r="F13">
-        <v>61.60769999999999</v>
+        <v>67.20839999999998</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2353,28 +2353,28 @@
         <v>48.3</v>
       </c>
       <c r="M13">
-        <v>3.09886731</v>
+        <v>3.380582519999999</v>
       </c>
       <c r="N13">
-        <v>45.20113268999999</v>
+        <v>44.91941748</v>
       </c>
       <c r="O13">
-        <v>4.520113268999999</v>
+        <v>4.491941748</v>
       </c>
       <c r="P13">
-        <v>40.68101942099999</v>
+        <v>40.427475732</v>
       </c>
       <c r="Q13">
-        <v>50.381019421</v>
+        <v>50.127475732</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1576924521252452</v>
+        <v>0.1588495346571038</v>
       </c>
       <c r="T13">
-        <v>0.684320308297272</v>
+        <v>0.6913968810230229</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.58634015859169</v>
+        <v>14.28747847870905</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1452199904982514</v>
+        <v>0.1451139986050345</v>
       </c>
       <c r="C14">
-        <v>501.7710992155074</v>
+        <v>496.7776370185414</v>
       </c>
       <c r="D14">
-        <v>568.9794992155074</v>
+        <v>569.5867370185414</v>
       </c>
       <c r="E14">
-        <v>64.93839999999999</v>
+        <v>70.5391</v>
       </c>
       <c r="F14">
-        <v>67.20839999999998</v>
+        <v>72.8091</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2435,28 +2435,28 @@
         <v>48.3</v>
       </c>
       <c r="M14">
-        <v>3.380582519999999</v>
+        <v>3.66229773</v>
       </c>
       <c r="N14">
-        <v>44.91941748</v>
+        <v>44.63770227</v>
       </c>
       <c r="O14">
-        <v>4.491941748</v>
+        <v>4.463770227</v>
       </c>
       <c r="P14">
-        <v>40.427475732</v>
+        <v>40.173932043</v>
       </c>
       <c r="Q14">
-        <v>50.127475732</v>
+        <v>49.873932043</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1588495346571038</v>
+        <v>0.160033216787396</v>
       </c>
       <c r="T14">
-        <v>0.6913968810230229</v>
+        <v>0.6986361335815495</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.28747847870905</v>
+        <v>13.18844167265451</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1451139986050345</v>
+        <v>0.1451970067118176</v>
       </c>
       <c r="C15">
-        <v>496.7776370185414</v>
+        <v>490.7012655848355</v>
       </c>
       <c r="D15">
-        <v>569.5867370185414</v>
+        <v>569.1110655848355</v>
       </c>
       <c r="E15">
-        <v>70.5391</v>
+        <v>76.13980000000001</v>
       </c>
       <c r="F15">
-        <v>72.8091</v>
+        <v>78.4098</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2517,45 +2517,45 @@
         <v>48.3</v>
       </c>
       <c r="M15">
-        <v>3.66229773</v>
+        <v>4.06162764</v>
       </c>
       <c r="N15">
-        <v>44.63770227</v>
+        <v>44.23837236</v>
       </c>
       <c r="O15">
-        <v>4.463770227</v>
+        <v>4.423837236</v>
       </c>
       <c r="P15">
-        <v>40.173932043</v>
+        <v>39.814535124</v>
       </c>
       <c r="Q15">
-        <v>49.873932043</v>
+        <v>49.51453512400001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.160033216787396</v>
+        <v>0.1612444264090903</v>
       </c>
       <c r="T15">
-        <v>0.6986361335815495</v>
+        <v>0.7060437408507396</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.18844167265451</v>
+        <v>11.89178434879865</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1451970067118176</v>
+        <v>0.1451045148186008</v>
       </c>
       <c r="C16">
-        <v>490.7012655848355</v>
+        <v>485.6306337292973</v>
       </c>
       <c r="D16">
-        <v>569.1110655848355</v>
+        <v>569.6411337292973</v>
       </c>
       <c r="E16">
-        <v>76.13980000000001</v>
+        <v>81.74050000000001</v>
       </c>
       <c r="F16">
-        <v>78.4098</v>
+        <v>84.01050000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2599,28 +2599,28 @@
         <v>48.3</v>
       </c>
       <c r="M16">
-        <v>4.06162764</v>
+        <v>4.351743900000001</v>
       </c>
       <c r="N16">
-        <v>44.23837236</v>
+        <v>43.94825609999999</v>
       </c>
       <c r="O16">
-        <v>4.423837236</v>
+        <v>4.39482561</v>
       </c>
       <c r="P16">
-        <v>39.814535124</v>
+        <v>39.55343049</v>
       </c>
       <c r="Q16">
-        <v>49.51453512400001</v>
+        <v>49.25343049</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1612444264090903</v>
+        <v>0.1624841350807068</v>
       </c>
       <c r="T16">
-        <v>0.7060437408507396</v>
+        <v>0.7136256447615579</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.89178434879865</v>
+        <v>11.09899872554541</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1451045148186008</v>
+        <v>0.1450120229253839</v>
       </c>
       <c r="C17">
-        <v>485.6306337292973</v>
+        <v>480.5609902016812</v>
       </c>
       <c r="D17">
-        <v>569.6411337292973</v>
+        <v>570.1721902016812</v>
       </c>
       <c r="E17">
-        <v>81.7405</v>
+        <v>87.3412</v>
       </c>
       <c r="F17">
-        <v>84.01049999999999</v>
+        <v>89.6112</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2681,28 +2681,28 @@
         <v>48.3</v>
       </c>
       <c r="M17">
-        <v>4.3517439</v>
+        <v>4.641860159999999</v>
       </c>
       <c r="N17">
-        <v>43.94825609999999</v>
+        <v>43.65813984</v>
       </c>
       <c r="O17">
-        <v>4.39482561</v>
+        <v>4.365813984</v>
       </c>
       <c r="P17">
-        <v>39.55343049</v>
+        <v>39.292325856</v>
       </c>
       <c r="Q17">
-        <v>49.25343049</v>
+        <v>48.992325856</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1624841350807068</v>
+        <v>0.1637533606254571</v>
       </c>
       <c r="T17">
-        <v>0.7136256447615579</v>
+        <v>0.721388070194062</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.09899872554541</v>
+        <v>10.40531130519882</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1450120229253839</v>
+        <v>0.1451796310321671</v>
       </c>
       <c r="C18">
-        <v>480.5609902016812</v>
+        <v>473.9986697936806</v>
       </c>
       <c r="D18">
-        <v>570.1721902016812</v>
+        <v>569.2105697936806</v>
       </c>
       <c r="E18">
-        <v>87.3412</v>
+        <v>92.9419</v>
       </c>
       <c r="F18">
-        <v>89.6112</v>
+        <v>95.2119</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2763,45 +2763,45 @@
         <v>48.3</v>
       </c>
       <c r="M18">
-        <v>4.641860159999999</v>
+        <v>5.09383665</v>
       </c>
       <c r="N18">
-        <v>43.65813984</v>
+        <v>43.20616335</v>
       </c>
       <c r="O18">
-        <v>4.365813984</v>
+        <v>4.320616335</v>
       </c>
       <c r="P18">
-        <v>39.292325856</v>
+        <v>38.885547015</v>
       </c>
       <c r="Q18">
-        <v>48.992325856</v>
+        <v>48.585547015</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1637533606254571</v>
+        <v>0.1650531699182736</v>
       </c>
       <c r="T18">
-        <v>0.721388070194062</v>
+        <v>0.7293375420225302</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.40531130519882</v>
+        <v>9.482047289443409</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1451796310321671</v>
+        <v>0.1451024391389502</v>
       </c>
       <c r="C19">
-        <v>473.9986697936806</v>
+        <v>468.8404407128485</v>
       </c>
       <c r="D19">
-        <v>569.2105697936806</v>
+        <v>569.6530407128485</v>
       </c>
       <c r="E19">
-        <v>92.9419</v>
+        <v>98.54260000000001</v>
       </c>
       <c r="F19">
-        <v>95.2119</v>
+        <v>100.8126</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2845,28 +2845,28 @@
         <v>48.3</v>
       </c>
       <c r="M19">
-        <v>5.09383665</v>
+        <v>5.3934741</v>
       </c>
       <c r="N19">
-        <v>43.20616335</v>
+        <v>42.9065259</v>
       </c>
       <c r="O19">
-        <v>4.320616335</v>
+        <v>4.29065259</v>
       </c>
       <c r="P19">
-        <v>38.885547015</v>
+        <v>38.61587331</v>
       </c>
       <c r="Q19">
-        <v>48.585547015</v>
+        <v>48.31587331</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1650531699182736</v>
+        <v>0.1663846818767686</v>
       </c>
       <c r="T19">
-        <v>0.7293375420225302</v>
+        <v>0.7374809034077903</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.482047289443409</v>
+        <v>8.955266884474332</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1451024391389502</v>
+        <v>0.1450252472457334</v>
       </c>
       <c r="C20">
-        <v>468.8404407128484</v>
+        <v>463.6829000690601</v>
       </c>
       <c r="D20">
-        <v>569.6530407128483</v>
+        <v>570.09620006906</v>
       </c>
       <c r="E20">
-        <v>98.54259999999999</v>
+        <v>104.1433</v>
       </c>
       <c r="F20">
-        <v>100.8126</v>
+        <v>106.4133</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2927,28 +2927,28 @@
         <v>48.3</v>
       </c>
       <c r="M20">
-        <v>5.3934741</v>
+        <v>5.693111549999999</v>
       </c>
       <c r="N20">
-        <v>42.9065259</v>
+        <v>42.60688845</v>
       </c>
       <c r="O20">
-        <v>4.29065259</v>
+        <v>4.260688845</v>
       </c>
       <c r="P20">
-        <v>38.61587331</v>
+        <v>38.346199605</v>
       </c>
       <c r="Q20">
-        <v>48.31587331</v>
+        <v>48.04619960500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1663846818767686</v>
+        <v>0.1677490706737449</v>
       </c>
       <c r="T20">
-        <v>0.7374809034077903</v>
+        <v>0.7458253354445383</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.955266884474332</v>
+        <v>8.483937048449366</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1450252472457334</v>
+        <v>0.1449480553525165</v>
       </c>
       <c r="C21">
-        <v>463.6829000690601</v>
+        <v>458.5260494702673</v>
       </c>
       <c r="D21">
-        <v>570.09620006906</v>
+        <v>570.5400494702673</v>
       </c>
       <c r="E21">
-        <v>104.1433</v>
+        <v>109.744</v>
       </c>
       <c r="F21">
-        <v>106.4133</v>
+        <v>112.014</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3009,28 +3009,28 @@
         <v>48.3</v>
       </c>
       <c r="M21">
-        <v>5.693111549999999</v>
+        <v>5.992749</v>
       </c>
       <c r="N21">
-        <v>42.60688845</v>
+        <v>42.30725099999999</v>
       </c>
       <c r="O21">
-        <v>4.260688845</v>
+        <v>4.2307251</v>
       </c>
       <c r="P21">
-        <v>38.346199605</v>
+        <v>38.07652589999999</v>
       </c>
       <c r="Q21">
-        <v>48.04619960500001</v>
+        <v>47.7765259</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1677490706737449</v>
+        <v>0.1691475691906456</v>
       </c>
       <c r="T21">
-        <v>0.7458253354445383</v>
+        <v>0.7543783782822051</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.483937048449366</v>
+        <v>8.059740196026898</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1449480553525165</v>
+        <v>0.1448708634592996</v>
       </c>
       <c r="C22">
-        <v>458.5260494702673</v>
+        <v>453.369890529433</v>
       </c>
       <c r="D22">
-        <v>570.5400494702673</v>
+        <v>570.9845905294329</v>
       </c>
       <c r="E22">
-        <v>109.744</v>
+        <v>115.3447</v>
       </c>
       <c r="F22">
-        <v>112.014</v>
+        <v>117.6147</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3091,28 +3091,28 @@
         <v>48.3</v>
       </c>
       <c r="M22">
-        <v>5.992749</v>
+        <v>6.29238645</v>
       </c>
       <c r="N22">
-        <v>42.30725099999999</v>
+        <v>42.00761354999999</v>
       </c>
       <c r="O22">
-        <v>4.2307251</v>
+        <v>4.200761355</v>
       </c>
       <c r="P22">
-        <v>38.07652589999999</v>
+        <v>37.806852195</v>
       </c>
       <c r="Q22">
-        <v>47.7765259</v>
+        <v>47.506852195</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1691475691906456</v>
+        <v>0.1705814727332907</v>
       </c>
       <c r="T22">
-        <v>0.7543783782822051</v>
+        <v>0.7631479538499393</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.059740196026898</v>
+        <v>7.675943043835141</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1448708634592996</v>
+        <v>0.1449520715660828</v>
       </c>
       <c r="C23">
-        <v>453.369890529433</v>
+        <v>447.3015394065984</v>
       </c>
       <c r="D23">
-        <v>570.9845905294329</v>
+        <v>570.5169394065983</v>
       </c>
       <c r="E23">
-        <v>115.3447</v>
+        <v>120.9454</v>
       </c>
       <c r="F23">
-        <v>117.6147</v>
+        <v>123.2154</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3173,45 +3173,45 @@
         <v>48.3</v>
       </c>
       <c r="M23">
-        <v>6.292386449999999</v>
+        <v>6.69059622</v>
       </c>
       <c r="N23">
-        <v>42.00761355</v>
+        <v>41.60940377999999</v>
       </c>
       <c r="O23">
-        <v>4.200761355</v>
+        <v>4.160940377999999</v>
       </c>
       <c r="P23">
-        <v>37.806852195</v>
+        <v>37.44846340199999</v>
       </c>
       <c r="Q23">
-        <v>47.50685219500001</v>
+        <v>47.148463402</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1705814727332907</v>
+        <v>0.1720521430334395</v>
       </c>
       <c r="T23">
-        <v>0.7631479538499393</v>
+        <v>0.7721423903296667</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.1</v>
       </c>
       <c r="W23">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.675943043835143</v>
+        <v>7.219087568850478</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1449520715660828</v>
+        <v>0.144882079672866</v>
       </c>
       <c r="C24">
-        <v>447.3015394065984</v>
+        <v>442.1038543698812</v>
       </c>
       <c r="D24">
-        <v>570.5169394065983</v>
+        <v>570.9199543698812</v>
       </c>
       <c r="E24">
-        <v>120.9454</v>
+        <v>126.5461</v>
       </c>
       <c r="F24">
-        <v>123.2154</v>
+        <v>128.8161</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3255,28 +3255,28 @@
         <v>48.3</v>
       </c>
       <c r="M24">
-        <v>6.69059622</v>
+        <v>6.994714229999999</v>
       </c>
       <c r="N24">
-        <v>41.60940377999999</v>
+        <v>41.30528577</v>
       </c>
       <c r="O24">
-        <v>4.160940377999999</v>
+        <v>4.130528577</v>
       </c>
       <c r="P24">
-        <v>37.44846340199999</v>
+        <v>37.174757193</v>
       </c>
       <c r="Q24">
-        <v>47.148463402</v>
+        <v>46.874757193</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1720521430334395</v>
+        <v>0.1735610125621636</v>
       </c>
       <c r="T24">
-        <v>0.7721423903296667</v>
+        <v>0.7813704485361403</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.219087568850478</v>
+        <v>6.905214196291762</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.144882079672866</v>
+        <v>0.1448120877796491</v>
       </c>
       <c r="C25">
-        <v>442.1038543698812</v>
+        <v>436.9067391177409</v>
       </c>
       <c r="D25">
-        <v>570.9199543698812</v>
+        <v>571.3235391177409</v>
       </c>
       <c r="E25">
-        <v>126.5461</v>
+        <v>132.1468</v>
       </c>
       <c r="F25">
-        <v>128.8161</v>
+        <v>134.4168</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3337,28 +3337,28 @@
         <v>48.3</v>
       </c>
       <c r="M25">
-        <v>6.994714229999999</v>
+        <v>7.29883224</v>
       </c>
       <c r="N25">
-        <v>41.30528577</v>
+        <v>41.00116775999999</v>
       </c>
       <c r="O25">
-        <v>4.130528577</v>
+        <v>4.100116775999999</v>
       </c>
       <c r="P25">
-        <v>37.174757193</v>
+        <v>36.90105098399999</v>
       </c>
       <c r="Q25">
-        <v>46.874757193</v>
+        <v>46.601050984</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1735610125621636</v>
+        <v>0.1751095891837488</v>
       </c>
       <c r="T25">
-        <v>0.7813704485361403</v>
+        <v>0.7908413503796264</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.905214196291762</v>
+        <v>6.617496938112938</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1448120877796491</v>
+        <v>0.1447420958864322</v>
       </c>
       <c r="C26">
-        <v>436.9067391177409</v>
+        <v>431.7101948593793</v>
       </c>
       <c r="D26">
-        <v>571.3235391177409</v>
+        <v>571.7276948593793</v>
       </c>
       <c r="E26">
-        <v>132.1468</v>
+        <v>137.7475</v>
       </c>
       <c r="F26">
-        <v>134.4168</v>
+        <v>140.0175</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3419,28 +3419,28 @@
         <v>48.3</v>
       </c>
       <c r="M26">
-        <v>7.298832239999999</v>
+        <v>7.602950249999999</v>
       </c>
       <c r="N26">
-        <v>41.00116776</v>
+        <v>40.69704975</v>
       </c>
       <c r="O26">
-        <v>4.100116776</v>
+        <v>4.069704975</v>
       </c>
       <c r="P26">
-        <v>36.901050984</v>
+        <v>36.627344775</v>
       </c>
       <c r="Q26">
-        <v>46.601050984</v>
+        <v>46.327344775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1751095891837488</v>
+        <v>0.1766994611819097</v>
       </c>
       <c r="T26">
-        <v>0.7908413503796264</v>
+        <v>0.8005648096056054</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.617496938112939</v>
+        <v>6.352797060588421</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1447420958864322</v>
+        <v>0.1449061039932154</v>
       </c>
       <c r="C27">
-        <v>431.7101948593793</v>
+        <v>425.1633576079761</v>
       </c>
       <c r="D27">
-        <v>571.7276948593793</v>
+        <v>570.7815576079761</v>
       </c>
       <c r="E27">
-        <v>137.7475</v>
+        <v>143.3482</v>
       </c>
       <c r="F27">
-        <v>140.0175</v>
+        <v>145.6182</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3501,45 +3501,45 @@
         <v>48.3</v>
       </c>
       <c r="M27">
-        <v>7.602950249999999</v>
+        <v>8.05268646</v>
       </c>
       <c r="N27">
-        <v>40.69704975</v>
+        <v>40.24731353999999</v>
       </c>
       <c r="O27">
-        <v>4.069704975</v>
+        <v>4.024731353999999</v>
       </c>
       <c r="P27">
-        <v>36.627344775</v>
+        <v>36.222582186</v>
       </c>
       <c r="Q27">
-        <v>46.327344775</v>
+        <v>45.922582186</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1766994611819097</v>
+        <v>0.1783323026935343</v>
       </c>
       <c r="T27">
-        <v>0.8005648096056054</v>
+        <v>0.8105510650268812</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.1</v>
       </c>
       <c r="W27">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.352797060588421</v>
+        <v>5.997998337563486</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1449061039932154</v>
+        <v>0.1448451120999985</v>
       </c>
       <c r="C28">
-        <v>425.1633576079761</v>
+        <v>419.9141443908539</v>
       </c>
       <c r="D28">
-        <v>570.7815576079761</v>
+        <v>571.1330443908539</v>
       </c>
       <c r="E28">
-        <v>143.3482</v>
+        <v>148.9489</v>
       </c>
       <c r="F28">
-        <v>145.6182</v>
+        <v>151.2189</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3583,28 +3583,28 @@
         <v>48.3</v>
       </c>
       <c r="M28">
-        <v>8.05268646</v>
+        <v>8.362405170000001</v>
       </c>
       <c r="N28">
-        <v>40.24731353999999</v>
+        <v>39.93759482999999</v>
       </c>
       <c r="O28">
-        <v>4.024731353999999</v>
+        <v>3.993759483</v>
       </c>
       <c r="P28">
-        <v>36.222582186</v>
+        <v>35.943835347</v>
       </c>
       <c r="Q28">
-        <v>45.922582186</v>
+        <v>45.643835347</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1783323026935343</v>
+        <v>0.1800098795890391</v>
       </c>
       <c r="T28">
-        <v>0.8105510650268812</v>
+        <v>0.820810916487096</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.997998337563486</v>
+        <v>5.775850250987061</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1448451120999985</v>
+        <v>0.1447841202067817</v>
       </c>
       <c r="C29">
-        <v>419.9141443908539</v>
+        <v>414.665364330975</v>
       </c>
       <c r="D29">
-        <v>571.1330443908539</v>
+        <v>571.484964330975</v>
       </c>
       <c r="E29">
-        <v>148.9489</v>
+        <v>154.5496</v>
       </c>
       <c r="F29">
-        <v>151.2189</v>
+        <v>156.8196</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3665,28 +3665,28 @@
         <v>48.3</v>
       </c>
       <c r="M29">
-        <v>8.362405170000001</v>
+        <v>8.672123880000001</v>
       </c>
       <c r="N29">
-        <v>39.93759482999999</v>
+        <v>39.62787612</v>
       </c>
       <c r="O29">
-        <v>3.993759483</v>
+        <v>3.962787612</v>
       </c>
       <c r="P29">
-        <v>35.943835347</v>
+        <v>35.665088508</v>
       </c>
       <c r="Q29">
-        <v>45.643835347</v>
+        <v>45.365088508</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1800098795890391</v>
+        <v>0.1817340558427523</v>
       </c>
       <c r="T29">
-        <v>0.820810916487096</v>
+        <v>0.8313557638212057</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.775850250987061</v>
+        <v>5.56956988488038</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1447841202067817</v>
+        <v>0.1447231283135648</v>
       </c>
       <c r="C30">
-        <v>414.665364330975</v>
+        <v>409.4170182295396</v>
       </c>
       <c r="D30">
-        <v>571.484964330975</v>
+        <v>571.8373182295396</v>
       </c>
       <c r="E30">
-        <v>154.5496</v>
+        <v>160.1503</v>
       </c>
       <c r="F30">
-        <v>156.8196</v>
+        <v>162.4203</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3747,28 +3747,28 @@
         <v>48.3</v>
       </c>
       <c r="M30">
-        <v>8.672123880000001</v>
+        <v>8.981842589999999</v>
       </c>
       <c r="N30">
-        <v>39.62787612</v>
+        <v>39.31815741</v>
       </c>
       <c r="O30">
-        <v>3.962787612</v>
+        <v>3.931815741</v>
       </c>
       <c r="P30">
-        <v>35.665088508</v>
+        <v>35.386341669</v>
       </c>
       <c r="Q30">
-        <v>45.365088508</v>
+        <v>45.086341669</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1817340558427523</v>
+        <v>0.1835068004416406</v>
       </c>
       <c r="T30">
-        <v>0.8313557638212057</v>
+        <v>0.8421976491083889</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.56956988488038</v>
+        <v>5.377515750918988</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1447231283135648</v>
+        <v>0.144662136420348</v>
       </c>
       <c r="C31">
-        <v>409.4170182295396</v>
+        <v>404.1691068897259</v>
       </c>
       <c r="D31">
-        <v>571.8373182295396</v>
+        <v>572.1901068897258</v>
       </c>
       <c r="E31">
-        <v>160.1503</v>
+        <v>165.751</v>
       </c>
       <c r="F31">
-        <v>162.4203</v>
+        <v>168.021</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3829,28 +3829,28 @@
         <v>48.3</v>
       </c>
       <c r="M31">
-        <v>8.981842589999999</v>
+        <v>9.2915613</v>
       </c>
       <c r="N31">
-        <v>39.31815741</v>
+        <v>39.0084387</v>
       </c>
       <c r="O31">
-        <v>3.931815741</v>
+        <v>3.90084387</v>
       </c>
       <c r="P31">
-        <v>35.386341669</v>
+        <v>35.10759483</v>
       </c>
       <c r="Q31">
-        <v>45.086341669</v>
+        <v>44.80759483</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1835068004416406</v>
+        <v>0.1853301948862114</v>
       </c>
       <c r="T31">
-        <v>0.8421976491083888</v>
+        <v>0.8533493025466343</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.377515750918988</v>
+        <v>5.198265225888355</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.144662136420348</v>
+        <v>0.1446011445271311</v>
       </c>
       <c r="C32">
-        <v>404.1691068897259</v>
+        <v>398.9216311166941</v>
       </c>
       <c r="D32">
-        <v>572.1901068897258</v>
+        <v>572.543331116694</v>
       </c>
       <c r="E32">
-        <v>165.751</v>
+        <v>171.3517</v>
       </c>
       <c r="F32">
-        <v>168.021</v>
+        <v>173.6217</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3911,28 +3911,28 @@
         <v>48.3</v>
       </c>
       <c r="M32">
-        <v>9.2915613</v>
+        <v>9.601280009999998</v>
       </c>
       <c r="N32">
-        <v>39.0084387</v>
+        <v>38.69871999</v>
       </c>
       <c r="O32">
-        <v>3.90084387</v>
+        <v>3.869871999</v>
       </c>
       <c r="P32">
-        <v>35.10759483</v>
+        <v>34.828847991</v>
       </c>
       <c r="Q32">
-        <v>44.80759483</v>
+        <v>44.52884799100001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1853301948862114</v>
+        <v>0.1872064413436683</v>
       </c>
       <c r="T32">
-        <v>0.8533493025466343</v>
+        <v>0.8648241923164233</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.198265225888355</v>
+        <v>5.0305792508597</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1446011445271311</v>
+        <v>0.1445401526339143</v>
       </c>
       <c r="C33">
-        <v>398.9216311166941</v>
+        <v>393.6745917175942</v>
       </c>
       <c r="D33">
-        <v>572.543331116694</v>
+        <v>572.8969917175942</v>
       </c>
       <c r="E33">
-        <v>171.3517</v>
+        <v>176.9524</v>
       </c>
       <c r="F33">
-        <v>173.6217</v>
+        <v>179.2224</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3993,28 +3993,28 @@
         <v>48.3</v>
       </c>
       <c r="M33">
-        <v>9.601280009999998</v>
+        <v>9.91099872</v>
       </c>
       <c r="N33">
-        <v>38.69871999</v>
+        <v>38.38900128</v>
       </c>
       <c r="O33">
-        <v>3.869871999</v>
+        <v>3.838900128</v>
       </c>
       <c r="P33">
-        <v>34.828847991</v>
+        <v>34.550101152</v>
       </c>
       <c r="Q33">
-        <v>44.52884799100001</v>
+        <v>44.250101152</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1872064413436683</v>
+        <v>0.1891378715204622</v>
       </c>
       <c r="T33">
-        <v>0.8648241923164233</v>
+        <v>0.8766365788441471</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.0305792508597</v>
+        <v>4.873373649270333</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1445401526339143</v>
+        <v>0.1444791607406974</v>
       </c>
       <c r="C34">
-        <v>393.6745917175942</v>
+        <v>388.4279895015724</v>
       </c>
       <c r="D34">
-        <v>572.8969917175942</v>
+        <v>573.2510895015723</v>
       </c>
       <c r="E34">
-        <v>176.9524</v>
+        <v>182.5531</v>
       </c>
       <c r="F34">
-        <v>179.2224</v>
+        <v>184.8231</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4075,28 +4075,28 @@
         <v>48.3</v>
       </c>
       <c r="M34">
-        <v>9.91099872</v>
+        <v>10.22071743</v>
       </c>
       <c r="N34">
-        <v>38.38900128</v>
+        <v>38.07928257</v>
       </c>
       <c r="O34">
-        <v>3.838900128</v>
+        <v>3.807928257</v>
       </c>
       <c r="P34">
-        <v>34.550101152</v>
+        <v>34.271354313</v>
       </c>
       <c r="Q34">
-        <v>44.250101152</v>
+        <v>43.971354313</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1891378715204622</v>
+        <v>0.1911269563293991</v>
       </c>
       <c r="T34">
-        <v>0.8766365788441471</v>
+        <v>0.8888015739249373</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.873373649270333</v>
+        <v>4.725695659898505</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1444791607406974</v>
+        <v>0.1444181688474805</v>
       </c>
       <c r="C35">
-        <v>388.4279895015724</v>
+        <v>383.1818252797756</v>
       </c>
       <c r="D35">
-        <v>573.2510895015723</v>
+        <v>573.6056252797756</v>
       </c>
       <c r="E35">
-        <v>182.5531</v>
+        <v>188.1538</v>
       </c>
       <c r="F35">
-        <v>184.8231</v>
+        <v>190.4238</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4157,28 +4157,28 @@
         <v>48.3</v>
       </c>
       <c r="M35">
-        <v>10.22071743</v>
+        <v>10.53043614</v>
       </c>
       <c r="N35">
-        <v>38.07928257</v>
+        <v>37.76956386</v>
       </c>
       <c r="O35">
-        <v>3.807928257</v>
+        <v>3.776956386</v>
       </c>
       <c r="P35">
-        <v>34.271354313</v>
+        <v>33.992607474</v>
       </c>
       <c r="Q35">
-        <v>43.971354313</v>
+        <v>43.692607474</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1911269563293991</v>
+        <v>0.1931763164355766</v>
       </c>
       <c r="T35">
-        <v>0.8888015739249373</v>
+        <v>0.9013352052202971</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.725695659898505</v>
+        <v>4.58670461107796</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1444181688474805</v>
+        <v>0.1451446769542637</v>
       </c>
       <c r="C36">
-        <v>383.1818252797756</v>
+        <v>373.3863445462893</v>
       </c>
       <c r="D36">
-        <v>573.6056252797756</v>
+        <v>569.4108445462892</v>
       </c>
       <c r="E36">
-        <v>188.1538</v>
+        <v>193.7545</v>
       </c>
       <c r="F36">
-        <v>190.4238</v>
+        <v>196.0245</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4239,45 +4239,45 @@
         <v>48.3</v>
       </c>
       <c r="M36">
-        <v>10.53043614</v>
+        <v>11.3302161</v>
       </c>
       <c r="N36">
-        <v>37.76956386</v>
+        <v>36.9697839</v>
       </c>
       <c r="O36">
-        <v>3.776956386</v>
+        <v>3.69697839</v>
       </c>
       <c r="P36">
-        <v>33.992607474</v>
+        <v>33.27280551</v>
       </c>
       <c r="Q36">
-        <v>43.692607474</v>
+        <v>42.97280551</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1931763164355766</v>
+        <v>0.1952887337757903</v>
       </c>
       <c r="T36">
-        <v>0.9013352052202971</v>
+        <v>0.91425448670936</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.1</v>
       </c>
       <c r="W36">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.58670461107796</v>
+        <v>4.262937226766574</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1451446769542637</v>
+        <v>0.1451061850610468</v>
       </c>
       <c r="C37">
-        <v>373.3863445462893</v>
+        <v>368.0063528678436</v>
       </c>
       <c r="D37">
-        <v>569.4108445462892</v>
+        <v>569.6315528678437</v>
       </c>
       <c r="E37">
-        <v>193.7545</v>
+        <v>199.3552</v>
       </c>
       <c r="F37">
-        <v>196.0245</v>
+        <v>201.6252</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4321,28 +4321,28 @@
         <v>48.3</v>
       </c>
       <c r="M37">
-        <v>11.3302161</v>
+        <v>11.65393656</v>
       </c>
       <c r="N37">
-        <v>36.9697839</v>
+        <v>36.64606343999999</v>
       </c>
       <c r="O37">
-        <v>3.69697839</v>
+        <v>3.664606343999999</v>
       </c>
       <c r="P37">
-        <v>33.27280551</v>
+        <v>32.98145709599999</v>
       </c>
       <c r="Q37">
-        <v>42.97280551</v>
+        <v>42.681457096</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1952887337757903</v>
+        <v>0.1974671641578857</v>
       </c>
       <c r="T37">
-        <v>0.91425448670936</v>
+        <v>0.9275774957449563</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.262937226766574</v>
+        <v>4.144522303800835</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1451061850610469</v>
+        <v>0.14506769316783</v>
       </c>
       <c r="C38">
-        <v>368.0063528678436</v>
+        <v>362.6265323524596</v>
       </c>
       <c r="D38">
-        <v>569.6315528678435</v>
+        <v>569.8524323524596</v>
       </c>
       <c r="E38">
-        <v>199.3552</v>
+        <v>204.9559</v>
       </c>
       <c r="F38">
-        <v>201.6252</v>
+        <v>207.2259</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4403,28 +4403,28 @@
         <v>48.3</v>
       </c>
       <c r="M38">
-        <v>11.65393656</v>
+        <v>11.97765702</v>
       </c>
       <c r="N38">
-        <v>36.64606344</v>
+        <v>36.32234298</v>
       </c>
       <c r="O38">
-        <v>3.664606344</v>
+        <v>3.632234298</v>
       </c>
       <c r="P38">
-        <v>32.981457096</v>
+        <v>32.690108682</v>
       </c>
       <c r="Q38">
-        <v>42.681457096</v>
+        <v>42.390108682</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1974671641578857</v>
+        <v>0.1997147510600476</v>
       </c>
       <c r="T38">
-        <v>0.9275774957449563</v>
+        <v>0.9413234574483491</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.144522303800837</v>
+        <v>4.032508187481896</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.14506769316783</v>
+        <v>0.1462262012746132</v>
       </c>
       <c r="C39">
-        <v>362.6265323524596</v>
+        <v>350.4520632148102</v>
       </c>
       <c r="D39">
-        <v>569.8524323524596</v>
+        <v>563.2786632148102</v>
       </c>
       <c r="E39">
-        <v>204.9559</v>
+        <v>210.5566</v>
       </c>
       <c r="F39">
-        <v>207.2259</v>
+        <v>212.8266</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4485,45 +4485,45 @@
         <v>48.3</v>
       </c>
       <c r="M39">
-        <v>11.97765702</v>
+        <v>13.04627058</v>
       </c>
       <c r="N39">
-        <v>36.32234298</v>
+        <v>35.25372942</v>
       </c>
       <c r="O39">
-        <v>3.632234298</v>
+        <v>3.525372942</v>
       </c>
       <c r="P39">
-        <v>32.690108682</v>
+        <v>31.728356478</v>
       </c>
       <c r="Q39">
-        <v>42.390108682</v>
+        <v>41.428356478</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1997147510600476</v>
+        <v>0.2020348407655051</v>
       </c>
       <c r="T39">
-        <v>0.9413234574483491</v>
+        <v>0.9555128372712065</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.1</v>
       </c>
       <c r="W39">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.032508187481896</v>
+        <v>3.702207439576192</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1462262012746132</v>
+        <v>0.1462192093813963</v>
       </c>
       <c r="C40">
-        <v>350.4520632148102</v>
+        <v>344.8905826459211</v>
       </c>
       <c r="D40">
-        <v>563.2786632148102</v>
+        <v>563.317882645921</v>
       </c>
       <c r="E40">
-        <v>210.5566</v>
+        <v>216.1573</v>
       </c>
       <c r="F40">
-        <v>212.8266</v>
+        <v>218.4273</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4567,28 +4567,28 @@
         <v>48.3</v>
       </c>
       <c r="M40">
-        <v>13.04627058</v>
+        <v>13.38959349</v>
       </c>
       <c r="N40">
-        <v>35.25372942</v>
+        <v>34.91040651</v>
       </c>
       <c r="O40">
-        <v>3.525372942</v>
+        <v>3.491040651</v>
       </c>
       <c r="P40">
-        <v>31.728356478</v>
+        <v>31.419365859</v>
       </c>
       <c r="Q40">
-        <v>41.428356478</v>
+        <v>41.11936585900001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2020348407655051</v>
+        <v>0.2044309989858956</v>
       </c>
       <c r="T40">
-        <v>0.9555128372712065</v>
+        <v>0.9701674426620261</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.702207439576192</v>
+        <v>3.607279043689623</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1462192093813963</v>
+        <v>0.1462122174881794</v>
       </c>
       <c r="C41">
-        <v>344.8905826459211</v>
+        <v>339.3291075388785</v>
       </c>
       <c r="D41">
-        <v>563.317882645921</v>
+        <v>563.3571075388785</v>
       </c>
       <c r="E41">
-        <v>216.1573</v>
+        <v>221.758</v>
       </c>
       <c r="F41">
-        <v>218.4273</v>
+        <v>224.028</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4649,28 +4649,28 @@
         <v>48.3</v>
       </c>
       <c r="M41">
-        <v>13.38959349</v>
+        <v>13.7329164</v>
       </c>
       <c r="N41">
-        <v>34.91040651</v>
+        <v>34.5670836</v>
       </c>
       <c r="O41">
-        <v>3.491040651</v>
+        <v>3.45670836</v>
       </c>
       <c r="P41">
-        <v>31.419365859</v>
+        <v>31.11037524</v>
       </c>
       <c r="Q41">
-        <v>41.11936585900001</v>
+        <v>40.81037524</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2044309989858956</v>
+        <v>0.2069070291469657</v>
       </c>
       <c r="T41">
-        <v>0.9701674426620261</v>
+        <v>0.9853105348992067</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.607279043689623</v>
+        <v>3.517097067597382</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1462122174881794</v>
+        <v>0.1472384255949626</v>
       </c>
       <c r="C42">
-        <v>339.3291075388785</v>
+        <v>328.0291705152412</v>
       </c>
       <c r="D42">
-        <v>563.3571075388785</v>
+        <v>557.6578705152411</v>
       </c>
       <c r="E42">
-        <v>221.758</v>
+        <v>227.3587</v>
       </c>
       <c r="F42">
-        <v>224.028</v>
+        <v>229.6287</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4731,45 +4731,45 @@
         <v>48.3</v>
       </c>
       <c r="M42">
-        <v>13.7329164</v>
+        <v>14.71919967</v>
       </c>
       <c r="N42">
-        <v>34.5670836</v>
+        <v>33.58080033</v>
       </c>
       <c r="O42">
-        <v>3.45670836</v>
+        <v>3.358080033</v>
       </c>
       <c r="P42">
-        <v>31.11037524</v>
+        <v>30.222720297</v>
       </c>
       <c r="Q42">
-        <v>40.81037524</v>
+        <v>39.922720297</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2069070291469657</v>
+        <v>0.2094669925338349</v>
       </c>
       <c r="T42">
-        <v>0.9853105348992067</v>
+        <v>1.00096695229697</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.517097067597382</v>
+        <v>3.281428412065287</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1472384255949626</v>
+        <v>0.1472566337017457</v>
       </c>
       <c r="C43">
-        <v>328.0291705152412</v>
+        <v>322.3283893900911</v>
       </c>
       <c r="D43">
-        <v>557.6578705152411</v>
+        <v>557.5577893900911</v>
       </c>
       <c r="E43">
-        <v>227.3587</v>
+        <v>232.9594</v>
       </c>
       <c r="F43">
-        <v>229.6287</v>
+        <v>235.2294</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4813,28 +4813,28 @@
         <v>48.3</v>
       </c>
       <c r="M43">
-        <v>14.71919967</v>
+        <v>15.07820454</v>
       </c>
       <c r="N43">
-        <v>33.58080033</v>
+        <v>33.22179546</v>
       </c>
       <c r="O43">
-        <v>3.358080033</v>
+        <v>3.322179546</v>
       </c>
       <c r="P43">
-        <v>30.222720297</v>
+        <v>29.89961591399999</v>
       </c>
       <c r="Q43">
-        <v>39.922720297</v>
+        <v>39.599615914</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2094669925338349</v>
+        <v>0.2121152305202513</v>
       </c>
       <c r="T43">
-        <v>1.00096695229697</v>
+        <v>1.017163246156724</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.281428412065287</v>
+        <v>3.20329916415897</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1472566337017457</v>
+        <v>0.1472748418085289</v>
       </c>
       <c r="C44">
-        <v>322.3283893900912</v>
+        <v>316.6276441809923</v>
       </c>
       <c r="D44">
-        <v>557.5577893900911</v>
+        <v>557.4577441809922</v>
       </c>
       <c r="E44">
-        <v>232.9594</v>
+        <v>238.5600999999999</v>
       </c>
       <c r="F44">
-        <v>235.2294</v>
+        <v>240.8301</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4895,28 +4895,28 @@
         <v>48.3</v>
       </c>
       <c r="M44">
-        <v>15.07820454</v>
+        <v>15.43720941</v>
       </c>
       <c r="N44">
-        <v>33.22179546</v>
+        <v>32.86279059</v>
       </c>
       <c r="O44">
-        <v>3.322179546</v>
+        <v>3.286279059</v>
       </c>
       <c r="P44">
-        <v>29.89961591399999</v>
+        <v>29.576511531</v>
       </c>
       <c r="Q44">
-        <v>39.599615914</v>
+        <v>39.276511531</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2121152305202512</v>
+        <v>0.2148563891377699</v>
       </c>
       <c r="T44">
-        <v>1.017163246156724</v>
+        <v>1.033927831029102</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.203299164158971</v>
+        <v>3.128803834759926</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1472748418085289</v>
+        <v>0.1472930499153121</v>
       </c>
       <c r="C45">
-        <v>316.6276441809923</v>
+        <v>310.9269348686146</v>
       </c>
       <c r="D45">
-        <v>557.4577441809922</v>
+        <v>557.3577348686146</v>
       </c>
       <c r="E45">
-        <v>238.5600999999999</v>
+        <v>244.1608</v>
       </c>
       <c r="F45">
-        <v>240.8301</v>
+        <v>246.4308</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4977,28 +4977,28 @@
         <v>48.3</v>
       </c>
       <c r="M45">
-        <v>15.43720941</v>
+        <v>15.79621428</v>
       </c>
       <c r="N45">
-        <v>32.86279059</v>
+        <v>32.50378572</v>
       </c>
       <c r="O45">
-        <v>3.286279059</v>
+        <v>3.250378572</v>
       </c>
       <c r="P45">
-        <v>29.576511531</v>
+        <v>29.253407148</v>
       </c>
       <c r="Q45">
-        <v>39.276511531</v>
+        <v>38.953407148</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2148563891377699</v>
+        <v>0.2176954462773429</v>
       </c>
       <c r="T45">
-        <v>1.033927831029102</v>
+        <v>1.051291151075493</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.128803834759926</v>
+        <v>3.057694656697199</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1472930499153121</v>
+        <v>0.1504702580220952</v>
       </c>
       <c r="C46">
-        <v>310.9269348686146</v>
+        <v>288.4079474098312</v>
       </c>
       <c r="D46">
-        <v>557.3577348686146</v>
+        <v>540.4394474098311</v>
       </c>
       <c r="E46">
-        <v>244.1608</v>
+        <v>249.7615</v>
       </c>
       <c r="F46">
-        <v>246.4308</v>
+        <v>252.0315</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5059,45 +5059,45 @@
         <v>48.3</v>
       </c>
       <c r="M46">
-        <v>15.79621428</v>
+        <v>18.12106485</v>
       </c>
       <c r="N46">
-        <v>32.50378572</v>
+        <v>30.17893515</v>
       </c>
       <c r="O46">
-        <v>3.250378572</v>
+        <v>3.017893515</v>
       </c>
       <c r="P46">
-        <v>29.253407148</v>
+        <v>27.161041635</v>
       </c>
       <c r="Q46">
-        <v>38.953407148</v>
+        <v>36.861041635</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2176954462773429</v>
+        <v>0.2206377418583549</v>
       </c>
       <c r="T46">
-        <v>1.051291151075493</v>
+        <v>1.069285864578116</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.1</v>
       </c>
       <c r="W46">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.057694656697199</v>
+        <v>2.665406277159259</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1504702580220952</v>
+        <v>0.1505586661288783</v>
       </c>
       <c r="C47">
-        <v>288.4079474098312</v>
+        <v>282.3511588575233</v>
       </c>
       <c r="D47">
-        <v>540.4394474098311</v>
+        <v>539.9833588575233</v>
       </c>
       <c r="E47">
-        <v>249.7615</v>
+        <v>255.3621999999999</v>
       </c>
       <c r="F47">
-        <v>252.0315</v>
+        <v>257.6322</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5141,28 +5141,28 @@
         <v>48.3</v>
       </c>
       <c r="M47">
-        <v>18.12106485</v>
+        <v>18.52375518</v>
       </c>
       <c r="N47">
-        <v>30.17893515</v>
+        <v>29.77624482</v>
       </c>
       <c r="O47">
-        <v>3.017893515</v>
+        <v>2.977624482</v>
       </c>
       <c r="P47">
-        <v>27.161041635</v>
+        <v>26.798620338</v>
       </c>
       <c r="Q47">
-        <v>36.861041635</v>
+        <v>36.498620338</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2206377418583549</v>
+        <v>0.2236890113497746</v>
       </c>
       <c r="T47">
-        <v>1.069285864578116</v>
+        <v>1.087947048951207</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.665406277159259</v>
+        <v>2.607462662438405</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1505586661288783</v>
+        <v>0.1506470742356615</v>
       </c>
       <c r="C48">
-        <v>282.3511588575233</v>
+        <v>276.2951394621178</v>
       </c>
       <c r="D48">
-        <v>539.9833588575233</v>
+        <v>539.5280394621178</v>
       </c>
       <c r="E48">
-        <v>255.3621999999999</v>
+        <v>260.9629</v>
       </c>
       <c r="F48">
-        <v>257.6322</v>
+        <v>263.2329</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5223,28 +5223,28 @@
         <v>48.3</v>
       </c>
       <c r="M48">
-        <v>18.52375518</v>
+        <v>18.92644551</v>
       </c>
       <c r="N48">
-        <v>29.77624482</v>
+        <v>29.37355449</v>
       </c>
       <c r="O48">
-        <v>2.977624482</v>
+        <v>2.937355449</v>
       </c>
       <c r="P48">
-        <v>26.798620338</v>
+        <v>26.43619904099999</v>
       </c>
       <c r="Q48">
-        <v>36.498620338</v>
+        <v>36.136199041</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2236890113497746</v>
+        <v>0.2268554230861538</v>
       </c>
       <c r="T48">
-        <v>1.087947048951207</v>
+        <v>1.107312428961019</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.607462662438405</v>
+        <v>2.551984733450354</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1506470742356615</v>
+        <v>0.1524202823424446</v>
       </c>
       <c r="C49">
-        <v>276.2951394621178</v>
+        <v>261.7215173089172</v>
       </c>
       <c r="D49">
-        <v>539.5280394621178</v>
+        <v>530.5551173089171</v>
       </c>
       <c r="E49">
-        <v>260.9629</v>
+        <v>266.5636</v>
       </c>
       <c r="F49">
-        <v>263.2329</v>
+        <v>268.8336</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5305,45 +5305,45 @@
         <v>48.3</v>
       </c>
       <c r="M49">
-        <v>18.92644551</v>
+        <v>20.37758688</v>
       </c>
       <c r="N49">
-        <v>29.37355449</v>
+        <v>27.92241311999999</v>
       </c>
       <c r="O49">
-        <v>2.937355449</v>
+        <v>2.792241312</v>
       </c>
       <c r="P49">
-        <v>26.43619904099999</v>
+        <v>25.13017180799999</v>
       </c>
       <c r="Q49">
-        <v>36.136199041</v>
+        <v>34.830171808</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2268554230861538</v>
+        <v>0.2301436198893166</v>
       </c>
       <c r="T49">
-        <v>1.107312428961019</v>
+        <v>1.1274226312789</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.1</v>
       </c>
       <c r="W49">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.551984733450354</v>
+        <v>2.370251212002193</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1524202823424446</v>
+        <v>0.1525437904492278</v>
       </c>
       <c r="C50">
-        <v>261.7215173089172</v>
+        <v>255.5069374962633</v>
       </c>
       <c r="D50">
-        <v>530.5551173089171</v>
+        <v>529.9412374962633</v>
       </c>
       <c r="E50">
-        <v>266.5636</v>
+        <v>272.1643</v>
       </c>
       <c r="F50">
-        <v>268.8335999999999</v>
+        <v>274.4343</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5387,28 +5387,28 @@
         <v>48.3</v>
       </c>
       <c r="M50">
-        <v>20.37758688</v>
+        <v>20.80211994</v>
       </c>
       <c r="N50">
-        <v>27.92241312</v>
+        <v>27.49788006</v>
       </c>
       <c r="O50">
-        <v>2.792241312</v>
+        <v>2.749788006</v>
       </c>
       <c r="P50">
-        <v>25.130171808</v>
+        <v>24.748092054</v>
       </c>
       <c r="Q50">
-        <v>34.830171808</v>
+        <v>34.448092054</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2301436198893166</v>
+        <v>0.2335607655867211</v>
       </c>
       <c r="T50">
-        <v>1.1274226312789</v>
+        <v>1.148321468981796</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.370251212002194</v>
+        <v>2.321878738287864</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1525437904492278</v>
+        <v>0.1526672985560109</v>
       </c>
       <c r="C51">
-        <v>255.5069374962633</v>
+        <v>249.2937766234437</v>
       </c>
       <c r="D51">
-        <v>529.9412374962633</v>
+        <v>529.3287766234437</v>
       </c>
       <c r="E51">
-        <v>272.1643</v>
+        <v>277.765</v>
       </c>
       <c r="F51">
-        <v>274.4343</v>
+        <v>280.035</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>48.3</v>
       </c>
       <c r="M51">
-        <v>20.80211994</v>
+        <v>21.226653</v>
       </c>
       <c r="N51">
-        <v>27.49788006</v>
+        <v>27.073347</v>
       </c>
       <c r="O51">
-        <v>2.749788006</v>
+        <v>2.7073347</v>
       </c>
       <c r="P51">
-        <v>24.748092054</v>
+        <v>24.3660123</v>
       </c>
       <c r="Q51">
-        <v>34.448092054</v>
+        <v>34.0660123</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2335607655867211</v>
+        <v>0.2371145971120218</v>
       </c>
       <c r="T51">
-        <v>1.148321468981796</v>
+        <v>1.170056260192808</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.321878738287864</v>
+        <v>2.275441163522106</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1526672985560109</v>
+        <v>0.152790806662794</v>
       </c>
       <c r="C52">
-        <v>249.2937766234437</v>
+        <v>243.0820297764689</v>
       </c>
       <c r="D52">
-        <v>529.3287766234437</v>
+        <v>528.7177297764689</v>
       </c>
       <c r="E52">
-        <v>277.765</v>
+        <v>283.3657</v>
       </c>
       <c r="F52">
-        <v>280.035</v>
+        <v>285.6357</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5551,28 +5551,28 @@
         <v>48.3</v>
       </c>
       <c r="M52">
-        <v>21.226653</v>
+        <v>21.65118606</v>
       </c>
       <c r="N52">
-        <v>27.073347</v>
+        <v>26.64881394</v>
       </c>
       <c r="O52">
-        <v>2.7073347</v>
+        <v>2.664881394</v>
       </c>
       <c r="P52">
-        <v>24.3660123</v>
+        <v>23.983932546</v>
       </c>
       <c r="Q52">
-        <v>34.0660123</v>
+        <v>33.683932546</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2371145971120218</v>
+        <v>0.240813482985294</v>
       </c>
       <c r="T52">
-        <v>1.170056260192808</v>
+        <v>1.192678185738963</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.275441163522106</v>
+        <v>2.230824670119711</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.152790806662794</v>
+        <v>0.1529143147695772</v>
       </c>
       <c r="C53">
-        <v>243.0820297764689</v>
+        <v>236.8716920640131</v>
       </c>
       <c r="D53">
-        <v>528.7177297764689</v>
+        <v>528.1080920640131</v>
       </c>
       <c r="E53">
-        <v>283.3657</v>
+        <v>288.9664</v>
       </c>
       <c r="F53">
-        <v>285.6357</v>
+        <v>291.2364</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5633,28 +5633,28 @@
         <v>48.3</v>
       </c>
       <c r="M53">
-        <v>21.65118606</v>
+        <v>22.07571912</v>
       </c>
       <c r="N53">
-        <v>26.64881394</v>
+        <v>26.22428087999999</v>
       </c>
       <c r="O53">
-        <v>2.664881394</v>
+        <v>2.622428087999999</v>
       </c>
       <c r="P53">
-        <v>23.983932546</v>
+        <v>23.601852792</v>
       </c>
       <c r="Q53">
-        <v>33.683932546</v>
+        <v>33.301852792</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.240813482985294</v>
+        <v>0.2446664891032858</v>
       </c>
       <c r="T53">
-        <v>1.192678185738963</v>
+        <v>1.216242691516208</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.230824670119711</v>
+        <v>2.187924195694332</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1529143147695772</v>
+        <v>0.1530378228763603</v>
       </c>
       <c r="C54">
-        <v>236.8716920640131</v>
+        <v>230.6627586172854</v>
       </c>
       <c r="D54">
-        <v>528.1080920640131</v>
+        <v>527.4998586172853</v>
       </c>
       <c r="E54">
-        <v>288.9664</v>
+        <v>294.5671</v>
       </c>
       <c r="F54">
-        <v>291.2364</v>
+        <v>296.8371</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5715,28 +5715,28 @@
         <v>48.3</v>
       </c>
       <c r="M54">
-        <v>22.07571912</v>
+        <v>22.50025218</v>
       </c>
       <c r="N54">
-        <v>26.22428087999999</v>
+        <v>25.79974782</v>
       </c>
       <c r="O54">
-        <v>2.622428087999999</v>
+        <v>2.579974782</v>
       </c>
       <c r="P54">
-        <v>23.601852792</v>
+        <v>23.219773038</v>
       </c>
       <c r="Q54">
-        <v>33.301852792</v>
+        <v>32.919773038</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2446664891032858</v>
+        <v>0.2486834529284263</v>
       </c>
       <c r="T54">
-        <v>1.216242691516208</v>
+        <v>1.240809942220145</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.187924195694332</v>
+        <v>2.146642607096326</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1530378228763603</v>
+        <v>0.1531613309831435</v>
       </c>
       <c r="C55">
-        <v>230.6627586172854</v>
+        <v>224.4552245898977</v>
       </c>
       <c r="D55">
-        <v>527.4998586172853</v>
+        <v>526.8930245898977</v>
       </c>
       <c r="E55">
-        <v>294.5671</v>
+        <v>300.1678</v>
       </c>
       <c r="F55">
-        <v>296.8371</v>
+        <v>302.4378</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5797,28 +5797,28 @@
         <v>48.3</v>
       </c>
       <c r="M55">
-        <v>22.50025218</v>
+        <v>22.92478524</v>
       </c>
       <c r="N55">
-        <v>25.79974782</v>
+        <v>25.37521476</v>
       </c>
       <c r="O55">
-        <v>2.579974782</v>
+        <v>2.537521476</v>
       </c>
       <c r="P55">
-        <v>23.219773038</v>
+        <v>22.837693284</v>
       </c>
       <c r="Q55">
-        <v>32.919773038</v>
+        <v>32.537693284</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2486834529284263</v>
+        <v>0.2528750673546598</v>
       </c>
       <c r="T55">
-        <v>1.240809942220145</v>
+        <v>1.266445334259035</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.146642607096326</v>
+        <v>2.106889966224172</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1531613309831435</v>
+        <v>0.1532848390899267</v>
       </c>
       <c r="C56">
-        <v>224.4552245898977</v>
+        <v>218.2490851577383</v>
       </c>
       <c r="D56">
-        <v>526.8930245898977</v>
+        <v>526.2875851577382</v>
       </c>
       <c r="E56">
-        <v>300.1678</v>
+        <v>305.7685</v>
       </c>
       <c r="F56">
-        <v>302.4378</v>
+        <v>308.0385</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5879,28 +5879,28 @@
         <v>48.3</v>
       </c>
       <c r="M56">
-        <v>22.92478524</v>
+        <v>23.3493183</v>
       </c>
       <c r="N56">
-        <v>25.37521476</v>
+        <v>24.9506817</v>
       </c>
       <c r="O56">
-        <v>2.537521476</v>
+        <v>2.49506817</v>
       </c>
       <c r="P56">
-        <v>22.837693284</v>
+        <v>22.45561353</v>
       </c>
       <c r="Q56">
-        <v>32.537693284</v>
+        <v>32.15561353</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2528750673546598</v>
+        <v>0.2572529757553926</v>
       </c>
       <c r="T56">
-        <v>1.266445334259035</v>
+        <v>1.293220077055209</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.106889966224172</v>
+        <v>2.068582875929187</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1532848390899267</v>
+        <v>0.1534083471967098</v>
       </c>
       <c r="C57">
-        <v>218.2490851577383</v>
+        <v>212.044335518843</v>
       </c>
       <c r="D57">
-        <v>526.2875851577382</v>
+        <v>525.683535518843</v>
       </c>
       <c r="E57">
-        <v>305.7685</v>
+        <v>311.3692</v>
       </c>
       <c r="F57">
-        <v>308.0385</v>
+        <v>313.6392</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5961,28 +5961,28 @@
         <v>48.3</v>
       </c>
       <c r="M57">
-        <v>23.3493183</v>
+        <v>23.77385136</v>
       </c>
       <c r="N57">
-        <v>24.9506817</v>
+        <v>24.52614864</v>
       </c>
       <c r="O57">
-        <v>2.49506817</v>
+        <v>2.452614864</v>
       </c>
       <c r="P57">
-        <v>22.45561353</v>
+        <v>22.07353377599999</v>
       </c>
       <c r="Q57">
-        <v>32.15561353</v>
+        <v>31.773533776</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2572529757553926</v>
+        <v>0.2618298799925222</v>
       </c>
       <c r="T57">
-        <v>1.293220077055209</v>
+        <v>1.321211853614845</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.068582875929187</v>
+        <v>2.03164389600188</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1534083471967098</v>
+        <v>0.1608164553034929</v>
       </c>
       <c r="C58">
-        <v>212.044335518843</v>
+        <v>172.5848241791641</v>
       </c>
       <c r="D58">
-        <v>525.683535518843</v>
+        <v>491.8247241791641</v>
       </c>
       <c r="E58">
-        <v>311.3692</v>
+        <v>316.9699</v>
       </c>
       <c r="F58">
-        <v>313.6392</v>
+        <v>319.2399</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6043,45 +6043,45 @@
         <v>48.3</v>
       </c>
       <c r="M58">
-        <v>23.77385136</v>
+        <v>28.731591</v>
       </c>
       <c r="N58">
-        <v>24.52614864</v>
+        <v>19.568409</v>
       </c>
       <c r="O58">
-        <v>2.452614864</v>
+        <v>1.9568409</v>
       </c>
       <c r="P58">
-        <v>22.07353377599999</v>
+        <v>17.6115681</v>
       </c>
       <c r="Q58">
-        <v>31.773533776</v>
+        <v>27.3115681</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2618298799925222</v>
+        <v>0.2666196634964952</v>
       </c>
       <c r="T58">
-        <v>1.321211853614845</v>
+        <v>1.350505573270279</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.1</v>
       </c>
       <c r="W58">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.03164389600188</v>
+        <v>1.681076415155708</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1608164553034929</v>
+        <v>0.1610677634102761</v>
       </c>
       <c r="C59">
-        <v>172.5848241791641</v>
+        <v>165.9118422449457</v>
       </c>
       <c r="D59">
-        <v>491.8247241791641</v>
+        <v>490.7524422449457</v>
       </c>
       <c r="E59">
-        <v>316.9699</v>
+        <v>322.5706</v>
       </c>
       <c r="F59">
-        <v>319.2399</v>
+        <v>324.8406</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6125,28 +6125,28 @@
         <v>48.3</v>
       </c>
       <c r="M59">
-        <v>28.731591</v>
+        <v>29.235654</v>
       </c>
       <c r="N59">
-        <v>19.568409</v>
+        <v>19.064346</v>
       </c>
       <c r="O59">
-        <v>1.9568409</v>
+        <v>1.9064346</v>
       </c>
       <c r="P59">
-        <v>17.6115681</v>
+        <v>17.1579114</v>
       </c>
       <c r="Q59">
-        <v>27.3115681</v>
+        <v>26.8579114</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2666196634964952</v>
+        <v>0.2716375319292288</v>
       </c>
       <c r="T59">
-        <v>1.350505573270279</v>
+        <v>1.381194231956924</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.681076415155708</v>
+        <v>1.652092339032334</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1610677634102761</v>
+        <v>0.1613190715170592</v>
       </c>
       <c r="C60">
-        <v>165.9118422449456</v>
+        <v>159.2435257419723</v>
       </c>
       <c r="D60">
-        <v>490.7524422449455</v>
+        <v>489.6848257419722</v>
       </c>
       <c r="E60">
-        <v>322.5706</v>
+        <v>328.1713</v>
       </c>
       <c r="F60">
-        <v>324.8405999999999</v>
+        <v>330.4413</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6207,28 +6207,28 @@
         <v>48.3</v>
       </c>
       <c r="M60">
-        <v>29.23565399999999</v>
+        <v>29.739717</v>
       </c>
       <c r="N60">
-        <v>19.064346</v>
+        <v>18.560283</v>
       </c>
       <c r="O60">
-        <v>1.906434600000001</v>
+        <v>1.8560283</v>
       </c>
       <c r="P60">
-        <v>17.1579114</v>
+        <v>16.7042547</v>
       </c>
       <c r="Q60">
-        <v>26.85791140000001</v>
+        <v>26.4042547</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2716375319292287</v>
+        <v>0.2769001744318517</v>
       </c>
       <c r="T60">
-        <v>1.381194231956924</v>
+        <v>1.41337989838438</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.652092339032334</v>
+        <v>1.624090773963989</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1613190715170592</v>
+        <v>0.1615703796238424</v>
       </c>
       <c r="C61">
-        <v>159.2435257419723</v>
+        <v>152.579844287843</v>
       </c>
       <c r="D61">
-        <v>489.6848257419722</v>
+        <v>488.621844287843</v>
       </c>
       <c r="E61">
-        <v>328.1713</v>
+        <v>333.772</v>
       </c>
       <c r="F61">
-        <v>330.4413</v>
+        <v>336.042</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6289,28 +6289,28 @@
         <v>48.3</v>
       </c>
       <c r="M61">
-        <v>29.739717</v>
+        <v>30.24378</v>
       </c>
       <c r="N61">
-        <v>18.560283</v>
+        <v>18.05622</v>
       </c>
       <c r="O61">
-        <v>1.8560283</v>
+        <v>1.805622</v>
       </c>
       <c r="P61">
-        <v>16.7042547</v>
+        <v>16.250598</v>
       </c>
       <c r="Q61">
-        <v>26.4042547</v>
+        <v>25.950598</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2769001744318517</v>
+        <v>0.2824259490596059</v>
       </c>
       <c r="T61">
-        <v>1.41337989838438</v>
+        <v>1.44717484813321</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.624090773963989</v>
+        <v>1.597022594397922</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1615703796238424</v>
+        <v>0.1618216877306255</v>
       </c>
       <c r="C62">
-        <v>152.579844287843</v>
+        <v>145.9207677633955</v>
       </c>
       <c r="D62">
-        <v>488.621844287843</v>
+        <v>487.5634677633954</v>
       </c>
       <c r="E62">
-        <v>333.772</v>
+        <v>339.3727</v>
       </c>
       <c r="F62">
-        <v>336.042</v>
+        <v>341.6426999999999</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6371,28 +6371,28 @@
         <v>48.3</v>
       </c>
       <c r="M62">
-        <v>30.24378</v>
+        <v>30.74784299999999</v>
       </c>
       <c r="N62">
-        <v>18.05622</v>
+        <v>17.552157</v>
       </c>
       <c r="O62">
-        <v>1.805622</v>
+        <v>1.755215700000001</v>
       </c>
       <c r="P62">
-        <v>16.250598</v>
+        <v>15.7969413</v>
       </c>
       <c r="Q62">
-        <v>25.950598</v>
+        <v>25.49694130000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2824259490596059</v>
+        <v>0.2882350967451937</v>
       </c>
       <c r="T62">
-        <v>1.44717484813321</v>
+        <v>1.482702872228133</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.597022594397922</v>
+        <v>1.570841896129104</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1618216877306255</v>
+        <v>0.1620729958374086</v>
       </c>
       <c r="C63">
-        <v>145.9207677633955</v>
+        <v>139.2662663098613</v>
       </c>
       <c r="D63">
-        <v>487.5634677633954</v>
+        <v>486.5096663098612</v>
       </c>
       <c r="E63">
-        <v>339.3727</v>
+        <v>344.9734</v>
       </c>
       <c r="F63">
-        <v>341.6426999999999</v>
+        <v>347.2434</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6453,28 +6453,28 @@
         <v>48.3</v>
       </c>
       <c r="M63">
-        <v>30.74784299999999</v>
+        <v>31.25190599999999</v>
       </c>
       <c r="N63">
-        <v>17.552157</v>
+        <v>17.048094</v>
       </c>
       <c r="O63">
-        <v>1.755215700000001</v>
+        <v>1.7048094</v>
       </c>
       <c r="P63">
-        <v>15.7969413</v>
+        <v>15.3432846</v>
       </c>
       <c r="Q63">
-        <v>25.49694130000001</v>
+        <v>25.04328460000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2882350967451937</v>
+        <v>0.2943499890458122</v>
       </c>
       <c r="T63">
-        <v>1.482702872228133</v>
+        <v>1.520100792328052</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.570841896129104</v>
+        <v>1.545505736514119</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1620729958374086</v>
+        <v>0.1623243039441918</v>
       </c>
       <c r="C64">
-        <v>139.2662663098613</v>
+        <v>132.6163103260574</v>
       </c>
       <c r="D64">
-        <v>486.5096663098612</v>
+        <v>485.4604103260573</v>
       </c>
       <c r="E64">
-        <v>344.9734</v>
+        <v>350.5741</v>
       </c>
       <c r="F64">
-        <v>347.2434</v>
+        <v>352.8441</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6535,28 +6535,28 @@
         <v>48.3</v>
       </c>
       <c r="M64">
-        <v>31.25190599999999</v>
+        <v>31.755969</v>
       </c>
       <c r="N64">
-        <v>17.048094</v>
+        <v>16.544031</v>
       </c>
       <c r="O64">
-        <v>1.7048094</v>
+        <v>1.6544031</v>
       </c>
       <c r="P64">
-        <v>15.3432846</v>
+        <v>14.8896279</v>
       </c>
       <c r="Q64">
-        <v>25.04328460000001</v>
+        <v>24.5896279</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2943499890458122</v>
+        <v>0.3007954160653832</v>
       </c>
       <c r="T64">
-        <v>1.520100792328052</v>
+        <v>1.559520221622562</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.545505736514119</v>
+        <v>1.520973899426593</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1623243039441918</v>
+        <v>0.1965927189311096</v>
       </c>
       <c r="C65">
-        <v>132.6163103260574</v>
+        <v>16.69225440611433</v>
       </c>
       <c r="D65">
-        <v>485.4604103260573</v>
+        <v>375.1370544061143</v>
       </c>
       <c r="E65">
-        <v>350.5741</v>
+        <v>356.1748</v>
       </c>
       <c r="F65">
-        <v>352.8441</v>
+        <v>358.4448</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6617,45 +6617,45 @@
         <v>48.3</v>
       </c>
       <c r="M65">
-        <v>31.755969</v>
+        <v>52.61969664</v>
       </c>
       <c r="N65">
-        <v>16.544031</v>
+        <v>-4.319696640000004</v>
       </c>
       <c r="O65">
-        <v>1.6544031</v>
+        <v>-0.4319696640000004</v>
       </c>
       <c r="P65">
-        <v>14.8896279</v>
+        <v>-3.887726976000003</v>
       </c>
       <c r="Q65">
-        <v>24.5896279</v>
+        <v>5.812273024</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3007954160653832</v>
+        <v>0.3090684470579399</v>
       </c>
       <c r="T65">
-        <v>1.559520221622562</v>
+        <v>1.61011704930708</v>
       </c>
       <c r="U65">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1</v>
+        <v>0.09179072302610675</v>
       </c>
       <c r="W65">
-        <v>0.081</v>
+        <v>0.1333251218597675</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.520973899426593</v>
+        <v>0.9179072302610675</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1965927189311096</v>
+        <v>0.1976027189311096</v>
       </c>
       <c r="C66">
-        <v>16.69225440611433</v>
+        <v>8.595627932477726</v>
       </c>
       <c r="D66">
-        <v>375.1370544061143</v>
+        <v>372.6411279324777</v>
       </c>
       <c r="E66">
-        <v>356.1748</v>
+        <v>361.7755</v>
       </c>
       <c r="F66">
-        <v>358.4448</v>
+        <v>364.0454999999999</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6699,37 +6699,37 @@
         <v>48.3</v>
       </c>
       <c r="M66">
-        <v>52.61969664</v>
+        <v>53.4418794</v>
       </c>
       <c r="N66">
-        <v>-4.319696640000004</v>
+        <v>-5.141879400000001</v>
       </c>
       <c r="O66">
-        <v>-0.4319696640000004</v>
+        <v>-0.5141879400000001</v>
       </c>
       <c r="P66">
-        <v>-3.887726976000003</v>
+        <v>-4.62769146</v>
       </c>
       <c r="Q66">
-        <v>5.812273024</v>
+        <v>5.072308540000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3090684470579399</v>
+        <v>0.3165904026881668</v>
       </c>
       <c r="T66">
-        <v>1.61011704930708</v>
+        <v>1.656120393572997</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.09179072302610675</v>
+        <v>0.09037855805647434</v>
       </c>
       <c r="W66">
-        <v>0.1333251218597675</v>
+        <v>0.1335324276773096</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9179072302610675</v>
+        <v>0.9037855805647433</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1976027189311096</v>
+        <v>0.1986127189311096</v>
       </c>
       <c r="C67">
-        <v>8.595627932477726</v>
+        <v>0.5319945991504369</v>
       </c>
       <c r="D67">
-        <v>372.6411279324777</v>
+        <v>370.1781945991504</v>
       </c>
       <c r="E67">
-        <v>361.7755</v>
+        <v>367.3762</v>
       </c>
       <c r="F67">
-        <v>364.0454999999999</v>
+        <v>369.6462</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6781,37 +6781,37 @@
         <v>48.3</v>
       </c>
       <c r="M67">
-        <v>53.4418794</v>
+        <v>54.26406216</v>
       </c>
       <c r="N67">
-        <v>-5.141879400000001</v>
+        <v>-5.964062160000005</v>
       </c>
       <c r="O67">
-        <v>-0.5141879400000001</v>
+        <v>-0.5964062160000004</v>
       </c>
       <c r="P67">
-        <v>-4.62769146</v>
+        <v>-5.367655944000004</v>
       </c>
       <c r="Q67">
-        <v>5.072308540000003</v>
+        <v>4.332344055999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3165904026881668</v>
+        <v>0.3245548262966423</v>
       </c>
       <c r="T67">
-        <v>1.656120393572997</v>
+        <v>1.704829816913379</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.09037855805647434</v>
+        <v>0.08900918596470958</v>
       </c>
       <c r="W67">
-        <v>0.1335324276773096</v>
+        <v>0.1337334515003807</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9037855805647433</v>
+        <v>0.8900918596470957</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1986127189311096</v>
+        <v>0.1996227189311096</v>
       </c>
       <c r="C68">
-        <v>0.5319945991504369</v>
+        <v>-7.499295492762997</v>
       </c>
       <c r="D68">
-        <v>370.1781945991504</v>
+        <v>367.747604507237</v>
       </c>
       <c r="E68">
-        <v>367.3762</v>
+        <v>372.9769</v>
       </c>
       <c r="F68">
-        <v>369.6462</v>
+        <v>375.2469</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6863,37 +6863,37 @@
         <v>48.3</v>
       </c>
       <c r="M68">
-        <v>54.26406216</v>
+        <v>55.08624492000001</v>
       </c>
       <c r="N68">
-        <v>-5.964062160000005</v>
+        <v>-6.786244920000009</v>
       </c>
       <c r="O68">
-        <v>-0.5964062160000004</v>
+        <v>-0.6786244920000009</v>
       </c>
       <c r="P68">
-        <v>-5.367655944000004</v>
+        <v>-6.107620428000008</v>
       </c>
       <c r="Q68">
-        <v>4.332344055999998</v>
+        <v>3.592379571999995</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3245548262966423</v>
+        <v>0.3330019422450254</v>
       </c>
       <c r="T68">
-        <v>1.704829816913379</v>
+        <v>1.756491326516815</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.08900918596470958</v>
+        <v>0.08768069065180345</v>
       </c>
       <c r="W68">
-        <v>0.1337334515003807</v>
+        <v>0.1339284746123152</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8900918596470957</v>
+        <v>0.8768069065180345</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1996227189311096</v>
+        <v>0.2006327189311096</v>
       </c>
       <c r="C69">
-        <v>-7.499295492762997</v>
+        <v>-15.49887528455668</v>
       </c>
       <c r="D69">
-        <v>367.747604507237</v>
+        <v>365.3487247154433</v>
       </c>
       <c r="E69">
-        <v>372.9769</v>
+        <v>378.5776</v>
       </c>
       <c r="F69">
-        <v>375.2469</v>
+        <v>380.8476</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6945,37 +6945,37 @@
         <v>48.3</v>
       </c>
       <c r="M69">
-        <v>55.08624492000001</v>
+        <v>55.90842768</v>
       </c>
       <c r="N69">
-        <v>-6.786244920000009</v>
+        <v>-7.608427680000005</v>
       </c>
       <c r="O69">
-        <v>-0.6786244920000009</v>
+        <v>-0.7608427680000006</v>
       </c>
       <c r="P69">
-        <v>-6.107620428000008</v>
+        <v>-6.847584912000005</v>
       </c>
       <c r="Q69">
-        <v>3.592379571999995</v>
+        <v>2.852415087999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3330019422450254</v>
+        <v>0.3419770029401824</v>
       </c>
       <c r="T69">
-        <v>1.756491326516815</v>
+        <v>1.811381680470465</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.08768069065180345</v>
+        <v>0.08639126873045341</v>
       </c>
       <c r="W69">
-        <v>0.1339284746123152</v>
+        <v>0.1341177617503694</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8768069065180345</v>
+        <v>0.863912687304534</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2006327189311096</v>
+        <v>0.2016427189311096</v>
       </c>
       <c r="C70">
-        <v>-15.49887528455668</v>
+        <v>-23.46736130942526</v>
       </c>
       <c r="D70">
-        <v>365.3487247154433</v>
+        <v>362.9809386905747</v>
       </c>
       <c r="E70">
-        <v>378.5776</v>
+        <v>384.1783</v>
       </c>
       <c r="F70">
-        <v>380.8476</v>
+        <v>386.4483</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7027,37 +7027,37 @@
         <v>48.3</v>
       </c>
       <c r="M70">
-        <v>55.90842768</v>
+        <v>56.73061044</v>
       </c>
       <c r="N70">
-        <v>-7.608427680000005</v>
+        <v>-8.430610440000002</v>
       </c>
       <c r="O70">
-        <v>-0.7608427680000006</v>
+        <v>-0.8430610440000003</v>
       </c>
       <c r="P70">
-        <v>-6.847584912000005</v>
+        <v>-7.587549396000002</v>
       </c>
       <c r="Q70">
-        <v>2.852415087999998</v>
+        <v>2.112450604000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3419770029401824</v>
+        <v>0.3515310998092206</v>
       </c>
       <c r="T70">
-        <v>1.811381680470465</v>
+        <v>1.869813347582416</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.08639126873045341</v>
+        <v>0.0851392213575483</v>
       </c>
       <c r="W70">
-        <v>0.1341177617503694</v>
+        <v>0.1343015623047119</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.863912687304534</v>
+        <v>0.8513922135754829</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2016427189311096</v>
+        <v>0.2026527189311096</v>
       </c>
       <c r="C71">
-        <v>-23.46736130942526</v>
+        <v>-31.40535422073589</v>
       </c>
       <c r="D71">
-        <v>362.9809386905747</v>
+        <v>360.6436457792641</v>
       </c>
       <c r="E71">
-        <v>384.1783</v>
+        <v>389.779</v>
       </c>
       <c r="F71">
-        <v>386.4483</v>
+        <v>392.049</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7109,37 +7109,37 @@
         <v>48.3</v>
       </c>
       <c r="M71">
-        <v>56.73061044</v>
+        <v>57.5527932</v>
       </c>
       <c r="N71">
-        <v>-8.430610440000002</v>
+        <v>-9.252793200000006</v>
       </c>
       <c r="O71">
-        <v>-0.8430610440000003</v>
+        <v>-0.9252793200000007</v>
       </c>
       <c r="P71">
-        <v>-7.587549396000002</v>
+        <v>-8.327513880000005</v>
       </c>
       <c r="Q71">
-        <v>2.112450604000001</v>
+        <v>1.372486119999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3515310998092206</v>
+        <v>0.3617221364695279</v>
       </c>
       <c r="T71">
-        <v>1.869813347582416</v>
+        <v>1.932140459168497</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.0851392213575483</v>
+        <v>0.08392294676672617</v>
       </c>
       <c r="W71">
-        <v>0.1343015623047119</v>
+        <v>0.1344801114146446</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8513922135754829</v>
+        <v>0.8392294676672616</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2026527189311096</v>
+        <v>0.2036627189311096</v>
       </c>
       <c r="C72">
-        <v>-31.40535422073589</v>
+        <v>-39.31343930002123</v>
       </c>
       <c r="D72">
-        <v>360.6436457792641</v>
+        <v>358.3362606999788</v>
       </c>
       <c r="E72">
-        <v>389.779</v>
+        <v>395.3797</v>
       </c>
       <c r="F72">
-        <v>392.049</v>
+        <v>397.6497</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7191,37 +7191,37 @@
         <v>48.3</v>
       </c>
       <c r="M72">
-        <v>57.5527932</v>
+        <v>58.37497596000001</v>
       </c>
       <c r="N72">
-        <v>-9.252793200000006</v>
+        <v>-10.07497596000001</v>
       </c>
       <c r="O72">
-        <v>-0.9252793200000007</v>
+        <v>-1.007497596000001</v>
       </c>
       <c r="P72">
-        <v>-8.327513880000005</v>
+        <v>-9.06747836400001</v>
       </c>
       <c r="Q72">
-        <v>1.372486119999998</v>
+        <v>0.6325216359999928</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3617221364695279</v>
+        <v>0.3726160032443393</v>
       </c>
       <c r="T72">
-        <v>1.932140459168497</v>
+        <v>1.998765992243273</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.08392294676672617</v>
+        <v>0.08274093343198353</v>
       </c>
       <c r="W72">
-        <v>0.1344801114146446</v>
+        <v>0.1346536309721848</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8392294676672616</v>
+        <v>0.8274093343198353</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2036627189311096</v>
+        <v>0.2046727189311096</v>
       </c>
       <c r="C73">
-        <v>-39.31343930002117</v>
+        <v>-47.19218694559532</v>
       </c>
       <c r="D73">
-        <v>358.3362606999788</v>
+        <v>356.0582130544046</v>
       </c>
       <c r="E73">
-        <v>395.3797</v>
+        <v>400.9804</v>
       </c>
       <c r="F73">
-        <v>397.6496999999999</v>
+        <v>403.2504</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7273,37 +7273,37 @@
         <v>48.3</v>
       </c>
       <c r="M73">
-        <v>58.37497595999999</v>
+        <v>59.19715872</v>
       </c>
       <c r="N73">
-        <v>-10.07497596</v>
+        <v>-10.89715872</v>
       </c>
       <c r="O73">
-        <v>-1.007497596</v>
+        <v>-1.089715872</v>
       </c>
       <c r="P73">
-        <v>-9.067478363999996</v>
+        <v>-9.807442848000001</v>
       </c>
       <c r="Q73">
-        <v>0.632521636000007</v>
+        <v>-0.107442847999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3726160032443392</v>
+        <v>0.3842880033602084</v>
       </c>
       <c r="T73">
-        <v>1.998765992243272</v>
+        <v>2.070150491966246</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.08274093343198356</v>
+        <v>0.08159175380098378</v>
       </c>
       <c r="W73">
-        <v>0.1346536309721848</v>
+        <v>0.1348223305420156</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8274093343198355</v>
+        <v>0.8159175380098378</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2046727189311096</v>
+        <v>0.2056827189311096</v>
       </c>
       <c r="C74">
-        <v>-47.19218694559532</v>
+        <v>-55.04215314265002</v>
       </c>
       <c r="D74">
-        <v>356.0582130544046</v>
+        <v>353.8089468573499</v>
       </c>
       <c r="E74">
-        <v>400.9804</v>
+        <v>406.5810999999999</v>
       </c>
       <c r="F74">
-        <v>403.2504</v>
+        <v>408.8510999999999</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7355,37 +7355,37 @@
         <v>48.3</v>
       </c>
       <c r="M74">
-        <v>59.19715872</v>
+        <v>60.01934147999999</v>
       </c>
       <c r="N74">
-        <v>-10.89715872</v>
+        <v>-11.71934148</v>
       </c>
       <c r="O74">
-        <v>-1.089715872</v>
+        <v>-1.171934148</v>
       </c>
       <c r="P74">
-        <v>-9.807442848000001</v>
+        <v>-10.547407332</v>
       </c>
       <c r="Q74">
-        <v>-0.107442847999998</v>
+        <v>-0.8474073319999942</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3842880033602084</v>
+        <v>0.3968245960772532</v>
       </c>
       <c r="T74">
-        <v>2.070150491966246</v>
+        <v>2.14682273240944</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.08159175380098378</v>
+        <v>0.08047405854343606</v>
       </c>
       <c r="W74">
-        <v>0.1348223305420156</v>
+        <v>0.1349864082058236</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8159175380098378</v>
+        <v>0.8047405854343606</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2056827189311096</v>
+        <v>0.2482434740252517</v>
       </c>
       <c r="C75">
-        <v>-55.04215314265002</v>
+        <v>-135.0259667985326</v>
       </c>
       <c r="D75">
-        <v>353.8089468573499</v>
+        <v>279.4258332014673</v>
       </c>
       <c r="E75">
-        <v>406.5810999999999</v>
+        <v>412.1818</v>
       </c>
       <c r="F75">
-        <v>408.8510999999999</v>
+        <v>414.4517999999999</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7437,45 +7437,45 @@
         <v>48.3</v>
       </c>
       <c r="M75">
-        <v>60.01934147999999</v>
+        <v>83.22192143999999</v>
       </c>
       <c r="N75">
-        <v>-11.71934148</v>
+        <v>-34.92192143999999</v>
       </c>
       <c r="O75">
-        <v>-1.171934148</v>
+        <v>-3.492192143999999</v>
       </c>
       <c r="P75">
-        <v>-10.547407332</v>
+        <v>-31.42972929599999</v>
       </c>
       <c r="Q75">
-        <v>-0.8474073319999942</v>
+        <v>-21.72972929599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3968245960772532</v>
+        <v>0.4164438309038481</v>
       </c>
       <c r="T75">
-        <v>2.14682273240944</v>
+        <v>2.266811530313913</v>
       </c>
       <c r="U75">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08047405854343606</v>
+        <v>0.05803759293736394</v>
       </c>
       <c r="W75">
-        <v>0.1349864082058236</v>
+        <v>0.1891460513381773</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8047405854343606</v>
+        <v>0.5803759293736394</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2482434740252517</v>
+        <v>0.2497934740252517</v>
       </c>
       <c r="C76">
-        <v>-135.0259667985326</v>
+        <v>-142.7498231569986</v>
       </c>
       <c r="D76">
-        <v>279.4258332014673</v>
+        <v>277.3026768430014</v>
       </c>
       <c r="E76">
-        <v>412.1818</v>
+        <v>417.7825</v>
       </c>
       <c r="F76">
-        <v>414.4517999999999</v>
+        <v>420.0525</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7519,37 +7519,37 @@
         <v>48.3</v>
       </c>
       <c r="M76">
-        <v>83.22192143999999</v>
+        <v>84.346542</v>
       </c>
       <c r="N76">
-        <v>-34.92192143999999</v>
+        <v>-36.046542</v>
       </c>
       <c r="O76">
-        <v>-3.492192143999999</v>
+        <v>-3.604654200000001</v>
       </c>
       <c r="P76">
-        <v>-31.42972929599999</v>
+        <v>-32.4418878</v>
       </c>
       <c r="Q76">
-        <v>-21.72972929599999</v>
+        <v>-22.7418878</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4164438309038481</v>
+        <v>0.431269584140002</v>
       </c>
       <c r="T76">
-        <v>2.266811530313913</v>
+        <v>2.35748399152647</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05803759293736394</v>
+        <v>0.05726375836486575</v>
       </c>
       <c r="W76">
-        <v>0.1891460513381773</v>
+        <v>0.189301437320335</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5803759293736394</v>
+        <v>0.5726375836486575</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2497934740252517</v>
+        <v>0.2513434740252518</v>
       </c>
       <c r="C77">
-        <v>-142.7498231569986</v>
+        <v>-150.4416581402181</v>
       </c>
       <c r="D77">
-        <v>277.3026768430014</v>
+        <v>275.2115418597819</v>
       </c>
       <c r="E77">
-        <v>417.7825</v>
+        <v>423.3832</v>
       </c>
       <c r="F77">
-        <v>420.0525</v>
+        <v>425.6532</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7601,37 +7601,37 @@
         <v>48.3</v>
       </c>
       <c r="M77">
-        <v>84.346542</v>
+        <v>85.47116256</v>
       </c>
       <c r="N77">
-        <v>-36.046542</v>
+        <v>-37.17116256</v>
       </c>
       <c r="O77">
-        <v>-3.604654200000001</v>
+        <v>-3.717116256</v>
       </c>
       <c r="P77">
-        <v>-32.4418878</v>
+        <v>-33.454046304</v>
       </c>
       <c r="Q77">
-        <v>-22.7418878</v>
+        <v>-23.754046304</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.431269584140002</v>
+        <v>0.4473308168125022</v>
       </c>
       <c r="T77">
-        <v>2.35748399152647</v>
+        <v>2.455712491173407</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05726375836486575</v>
+        <v>0.05651028786006488</v>
       </c>
       <c r="W77">
-        <v>0.189301437320335</v>
+        <v>0.189452734197699</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5726375836486575</v>
+        <v>0.5651028786006488</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2513434740252518</v>
+        <v>0.2528934740252518</v>
       </c>
       <c r="C78">
-        <v>-150.4416581402181</v>
+        <v>-158.1021907442655</v>
       </c>
       <c r="D78">
-        <v>275.2115418597819</v>
+        <v>273.1517092557345</v>
       </c>
       <c r="E78">
-        <v>423.3832</v>
+        <v>428.9839</v>
       </c>
       <c r="F78">
-        <v>425.6532</v>
+        <v>431.2539</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7683,37 +7683,37 @@
         <v>48.3</v>
       </c>
       <c r="M78">
-        <v>85.47116256</v>
+        <v>86.59578312000001</v>
       </c>
       <c r="N78">
-        <v>-37.17116256</v>
+        <v>-38.29578312000001</v>
       </c>
       <c r="O78">
-        <v>-3.717116256</v>
+        <v>-3.829578312000001</v>
       </c>
       <c r="P78">
-        <v>-33.454046304</v>
+        <v>-34.46620480800001</v>
       </c>
       <c r="Q78">
-        <v>-23.754046304</v>
+        <v>-24.766204808</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4473308168125022</v>
+        <v>0.4647886784130457</v>
       </c>
       <c r="T78">
-        <v>2.455712491173407</v>
+        <v>2.562482599485294</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05651028786006488</v>
+        <v>0.05577638801772637</v>
       </c>
       <c r="W78">
-        <v>0.189452734197699</v>
+        <v>0.1896001012860405</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5651028786006488</v>
+        <v>0.5577638801772637</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2528934740252518</v>
+        <v>0.2544434740252517</v>
       </c>
       <c r="C79">
-        <v>-158.1021907442655</v>
+        <v>-165.7321185996986</v>
       </c>
       <c r="D79">
-        <v>273.1517092557345</v>
+        <v>271.1224814003014</v>
       </c>
       <c r="E79">
-        <v>428.9839</v>
+        <v>434.5846</v>
       </c>
       <c r="F79">
-        <v>431.2539</v>
+        <v>436.8545999999999</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7765,37 +7765,37 @@
         <v>48.3</v>
       </c>
       <c r="M79">
-        <v>86.59578312000001</v>
+        <v>87.72040367999999</v>
       </c>
       <c r="N79">
-        <v>-38.29578312000001</v>
+        <v>-39.42040367999999</v>
       </c>
       <c r="O79">
-        <v>-3.829578312000001</v>
+        <v>-3.942040367999999</v>
       </c>
       <c r="P79">
-        <v>-34.46620480800001</v>
+        <v>-35.47836331199999</v>
       </c>
       <c r="Q79">
-        <v>-24.766204808</v>
+        <v>-25.77836331199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4647886784130457</v>
+        <v>0.4838336183409114</v>
       </c>
       <c r="T79">
-        <v>2.562482599485294</v>
+        <v>2.67895908128008</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.05577638801772637</v>
+        <v>0.05506130612006323</v>
       </c>
       <c r="W79">
-        <v>0.1896001012860405</v>
+        <v>0.1897436897310913</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5577638801772637</v>
+        <v>0.5506130612006321</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2544434740252517</v>
+        <v>0.2559934740252517</v>
       </c>
       <c r="C80">
-        <v>-165.7321185996986</v>
+        <v>-173.332118759322</v>
       </c>
       <c r="D80">
-        <v>271.1224814003014</v>
+        <v>269.123181240678</v>
       </c>
       <c r="E80">
-        <v>434.5846</v>
+        <v>440.1853</v>
       </c>
       <c r="F80">
-        <v>436.8545999999999</v>
+        <v>442.4553</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7847,37 +7847,37 @@
         <v>48.3</v>
       </c>
       <c r="M80">
-        <v>87.72040367999999</v>
+        <v>88.84502424</v>
       </c>
       <c r="N80">
-        <v>-39.42040367999999</v>
+        <v>-40.54502424</v>
       </c>
       <c r="O80">
-        <v>-3.942040367999999</v>
+        <v>-4.054502424000001</v>
       </c>
       <c r="P80">
-        <v>-35.47836331199999</v>
+        <v>-36.490521816</v>
       </c>
       <c r="Q80">
-        <v>-25.77836331199999</v>
+        <v>-26.790521816</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4838336183409114</v>
+        <v>0.5046923620714311</v>
       </c>
       <c r="T80">
-        <v>2.67895908128008</v>
+        <v>2.806528561341036</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05506130612006323</v>
+        <v>0.05436432756158141</v>
       </c>
       <c r="W80">
-        <v>0.1897436897310913</v>
+        <v>0.1898836430256345</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5506130612006321</v>
+        <v>0.543643275615814</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2559934740252517</v>
+        <v>0.2575434740252517</v>
       </c>
       <c r="C81">
-        <v>-173.332118759322</v>
+        <v>-180.9028484513507</v>
       </c>
       <c r="D81">
-        <v>269.123181240678</v>
+        <v>267.1531515486492</v>
       </c>
       <c r="E81">
-        <v>440.1853</v>
+        <v>445.786</v>
       </c>
       <c r="F81">
-        <v>442.4553</v>
+        <v>448.056</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7929,37 +7929,37 @@
         <v>48.3</v>
       </c>
       <c r="M81">
-        <v>88.84502424</v>
+        <v>89.9696448</v>
       </c>
       <c r="N81">
-        <v>-40.54502424</v>
+        <v>-41.6696448</v>
       </c>
       <c r="O81">
-        <v>-4.054502424000001</v>
+        <v>-4.16696448</v>
       </c>
       <c r="P81">
-        <v>-36.490521816</v>
+        <v>-37.50268032</v>
       </c>
       <c r="Q81">
-        <v>-26.790521816</v>
+        <v>-27.80268032</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5046923620714311</v>
+        <v>0.5276369801750026</v>
       </c>
       <c r="T81">
-        <v>2.806528561341036</v>
+        <v>2.946854989408088</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05436432756158141</v>
+        <v>0.05368477346706163</v>
       </c>
       <c r="W81">
-        <v>0.1898836430256345</v>
+        <v>0.190020097487814</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.543643275615814</v>
+        <v>0.5368477346706164</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2575434740252517</v>
+        <v>0.2590934740252517</v>
       </c>
       <c r="C82">
-        <v>-180.9028484513507</v>
+        <v>-188.4449457997355</v>
       </c>
       <c r="D82">
-        <v>267.1531515486492</v>
+        <v>265.2117542002645</v>
       </c>
       <c r="E82">
-        <v>445.786</v>
+        <v>451.3867</v>
       </c>
       <c r="F82">
-        <v>448.056</v>
+        <v>453.6567</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8011,37 +8011,37 @@
         <v>48.3</v>
       </c>
       <c r="M82">
-        <v>89.9696448</v>
+        <v>91.09426536000001</v>
       </c>
       <c r="N82">
-        <v>-41.6696448</v>
+        <v>-42.79426536000001</v>
       </c>
       <c r="O82">
-        <v>-4.16696448</v>
+        <v>-4.279426536000002</v>
       </c>
       <c r="P82">
-        <v>-37.50268032</v>
+        <v>-38.51483882400001</v>
       </c>
       <c r="Q82">
-        <v>-27.80268032</v>
+        <v>-28.81483882400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5276369801750026</v>
+        <v>0.5529968212368448</v>
       </c>
       <c r="T82">
-        <v>2.946854989408088</v>
+        <v>3.101952620429567</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.05368477346706163</v>
+        <v>0.0530219984859868</v>
       </c>
       <c r="W82">
-        <v>0.190020097487814</v>
+        <v>0.1901531827040139</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5368477346706164</v>
+        <v>0.5302199848598679</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2590934740252517</v>
+        <v>0.2606434740252518</v>
       </c>
       <c r="C83">
-        <v>-188.4449457997355</v>
+        <v>-195.9590305133066</v>
       </c>
       <c r="D83">
-        <v>265.2117542002645</v>
+        <v>263.2983694866934</v>
       </c>
       <c r="E83">
-        <v>451.3867</v>
+        <v>456.9874</v>
       </c>
       <c r="F83">
-        <v>453.6567</v>
+        <v>459.2574</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8093,37 +8093,37 @@
         <v>48.3</v>
       </c>
       <c r="M83">
-        <v>91.09426536000001</v>
+        <v>92.21888591999999</v>
       </c>
       <c r="N83">
-        <v>-42.79426536000001</v>
+        <v>-43.91888591999999</v>
       </c>
       <c r="O83">
-        <v>-4.279426536000002</v>
+        <v>-4.391888592</v>
       </c>
       <c r="P83">
-        <v>-38.51483882400001</v>
+        <v>-39.52699732799999</v>
       </c>
       <c r="Q83">
-        <v>-28.81483882400001</v>
+        <v>-29.82699732799999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5529968212368448</v>
+        <v>0.5811744224166696</v>
       </c>
       <c r="T83">
-        <v>3.101952620429567</v>
+        <v>3.274283321564543</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0530219984859868</v>
+        <v>0.05237538874835282</v>
       </c>
       <c r="W83">
-        <v>0.1901531827040139</v>
+        <v>0.1902830219393308</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5302199848598679</v>
+        <v>0.5237538874835281</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2606434740252518</v>
+        <v>0.2621934740252517</v>
       </c>
       <c r="C84">
-        <v>-195.9590305133066</v>
+        <v>-203.4457045452995</v>
       </c>
       <c r="D84">
-        <v>263.2983694866934</v>
+        <v>261.4123954547005</v>
       </c>
       <c r="E84">
-        <v>456.9874</v>
+        <v>462.5881</v>
       </c>
       <c r="F84">
-        <v>459.2574</v>
+        <v>464.8581</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8175,37 +8175,37 @@
         <v>48.3</v>
       </c>
       <c r="M84">
-        <v>92.21888591999999</v>
+        <v>93.34350648</v>
       </c>
       <c r="N84">
-        <v>-43.91888591999999</v>
+        <v>-45.04350648</v>
       </c>
       <c r="O84">
-        <v>-4.391888592</v>
+        <v>-4.504350648000001</v>
       </c>
       <c r="P84">
-        <v>-39.52699732799999</v>
+        <v>-40.53915583200001</v>
       </c>
       <c r="Q84">
-        <v>-29.82699732799999</v>
+        <v>-30.839155832</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5811744224166696</v>
+        <v>0.6126670355000031</v>
       </c>
       <c r="T84">
-        <v>3.274283321564543</v>
+        <v>3.466888222833046</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.05237538874835282</v>
+        <v>0.05174435996825218</v>
       </c>
       <c r="W84">
-        <v>0.1902830219393308</v>
+        <v>0.190409732518375</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5237538874835281</v>
+        <v>0.5174435996825217</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2621934740252517</v>
+        <v>0.2637434740252518</v>
       </c>
       <c r="C85">
-        <v>-203.4457045452995</v>
+        <v>-210.9055527247392</v>
       </c>
       <c r="D85">
-        <v>261.4123954547005</v>
+        <v>259.5532472752608</v>
       </c>
       <c r="E85">
-        <v>462.5881</v>
+        <v>468.1888</v>
       </c>
       <c r="F85">
-        <v>464.8581</v>
+        <v>470.4588</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8257,37 +8257,37 @@
         <v>48.3</v>
       </c>
       <c r="M85">
-        <v>93.34350648</v>
+        <v>94.46812704</v>
       </c>
       <c r="N85">
-        <v>-45.04350648</v>
+        <v>-46.16812704</v>
       </c>
       <c r="O85">
-        <v>-4.504350648000001</v>
+        <v>-4.616812704</v>
       </c>
       <c r="P85">
-        <v>-40.53915583200001</v>
+        <v>-41.551314336</v>
       </c>
       <c r="Q85">
-        <v>-30.839155832</v>
+        <v>-31.851314336</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6126670355000031</v>
+        <v>0.6480962252187534</v>
       </c>
       <c r="T85">
-        <v>3.466888222833046</v>
+        <v>3.683568736760111</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.05174435996825218</v>
+        <v>0.05112835568291584</v>
       </c>
       <c r="W85">
-        <v>0.190409732518375</v>
+        <v>0.1905334261788705</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5174435996825217</v>
+        <v>0.5112835568291585</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2637434740252517</v>
+        <v>0.2652934740252517</v>
       </c>
       <c r="C86">
-        <v>-210.905552724739</v>
+        <v>-218.3391433610701</v>
       </c>
       <c r="D86">
-        <v>259.5532472752609</v>
+        <v>257.7203566389299</v>
       </c>
       <c r="E86">
-        <v>468.1888</v>
+        <v>473.7895</v>
       </c>
       <c r="F86">
-        <v>470.4587999999999</v>
+        <v>476.0595</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8339,37 +8339,37 @@
         <v>48.3</v>
       </c>
       <c r="M86">
-        <v>94.46812703999998</v>
+        <v>95.5927476</v>
       </c>
       <c r="N86">
-        <v>-46.16812703999999</v>
+        <v>-47.2927476</v>
       </c>
       <c r="O86">
-        <v>-4.616812703999999</v>
+        <v>-4.72927476</v>
       </c>
       <c r="P86">
-        <v>-41.55131433599999</v>
+        <v>-42.56347284</v>
       </c>
       <c r="Q86">
-        <v>-31.85131433599999</v>
+        <v>-32.86347283999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.648096225218753</v>
+        <v>0.6882493069000033</v>
       </c>
       <c r="T86">
-        <v>3.683568736760109</v>
+        <v>3.92913998587745</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.05112835568291585</v>
+        <v>0.05052684561605802</v>
       </c>
       <c r="W86">
-        <v>0.1905334261788705</v>
+        <v>0.1906542094002956</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5112835568291585</v>
+        <v>0.50526845616058</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2652934740252517</v>
+        <v>0.2975853629199288</v>
       </c>
       <c r="C87">
-        <v>-218.3391433610701</v>
+        <v>-256.9929050083727</v>
       </c>
       <c r="D87">
-        <v>257.7203566389299</v>
+        <v>224.6672949916272</v>
       </c>
       <c r="E87">
-        <v>473.7895</v>
+        <v>479.3901999999999</v>
       </c>
       <c r="F87">
-        <v>476.0595</v>
+        <v>481.6601999999999</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8421,45 +8421,45 @@
         <v>48.3</v>
       </c>
       <c r="M87">
-        <v>95.5927476</v>
+        <v>113.57547516</v>
       </c>
       <c r="N87">
-        <v>-47.2927476</v>
+        <v>-65.27547515999998</v>
       </c>
       <c r="O87">
-        <v>-4.72927476</v>
+        <v>-6.527547515999998</v>
       </c>
       <c r="P87">
-        <v>-42.56347284</v>
+        <v>-58.74792764399999</v>
       </c>
       <c r="Q87">
-        <v>-32.86347283999999</v>
+        <v>-49.04792764399998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6882493069000033</v>
+        <v>0.7387234637834112</v>
       </c>
       <c r="T87">
-        <v>3.92913998587745</v>
+        <v>4.237833646115017</v>
       </c>
       <c r="U87">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05052684561605802</v>
+        <v>0.04252678664294132</v>
       </c>
       <c r="W87">
-        <v>0.1906542094002956</v>
+        <v>0.2257721837095945</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.50526845616058</v>
+        <v>0.4252678664294131</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2975853629199288</v>
+        <v>0.2994853629199288</v>
       </c>
       <c r="C88">
-        <v>-256.9929050083727</v>
+        <v>-264.2762715034784</v>
       </c>
       <c r="D88">
-        <v>224.6672949916272</v>
+        <v>222.9846284965216</v>
       </c>
       <c r="E88">
-        <v>479.3901999999999</v>
+        <v>484.9909</v>
       </c>
       <c r="F88">
-        <v>481.6601999999999</v>
+        <v>487.2608999999999</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8503,37 +8503,37 @@
         <v>48.3</v>
       </c>
       <c r="M88">
-        <v>113.57547516</v>
+        <v>114.89612022</v>
       </c>
       <c r="N88">
-        <v>-65.27547515999998</v>
+        <v>-66.59612021999999</v>
       </c>
       <c r="O88">
-        <v>-6.527547515999998</v>
+        <v>-6.659612021999999</v>
       </c>
       <c r="P88">
-        <v>-58.74792764399999</v>
+        <v>-59.93650819799999</v>
       </c>
       <c r="Q88">
-        <v>-49.04792764399998</v>
+        <v>-50.23650819799999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7387234637834112</v>
+        <v>0.7920252686898275</v>
       </c>
       <c r="T88">
-        <v>4.237833646115017</v>
+        <v>4.563820849662325</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04252678664294132</v>
+        <v>0.04203797300336727</v>
       </c>
       <c r="W88">
-        <v>0.2257721837095945</v>
+        <v>0.225887445965806</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4252678664294131</v>
+        <v>0.4203797300336727</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2994853629199288</v>
+        <v>0.3013853629199288</v>
       </c>
       <c r="C89">
-        <v>-264.2762715034784</v>
+        <v>-271.5346203973868</v>
       </c>
       <c r="D89">
-        <v>222.9846284965216</v>
+        <v>221.3269796026131</v>
       </c>
       <c r="E89">
-        <v>484.9909</v>
+        <v>490.5916</v>
       </c>
       <c r="F89">
-        <v>487.2608999999999</v>
+        <v>492.8616</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8585,37 +8585,37 @@
         <v>48.3</v>
       </c>
       <c r="M89">
-        <v>114.89612022</v>
+        <v>116.21676528</v>
       </c>
       <c r="N89">
-        <v>-66.59612021999999</v>
+        <v>-67.91676527999999</v>
       </c>
       <c r="O89">
-        <v>-6.659612021999999</v>
+        <v>-6.791676528</v>
       </c>
       <c r="P89">
-        <v>-59.93650819799999</v>
+        <v>-61.125088752</v>
       </c>
       <c r="Q89">
-        <v>-50.23650819799999</v>
+        <v>-51.42508875199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7920252686898275</v>
+        <v>0.8542107077473133</v>
       </c>
       <c r="T89">
-        <v>4.563820849662325</v>
+        <v>4.944139253800854</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04203797300336727</v>
+        <v>0.04156026876469265</v>
       </c>
       <c r="W89">
-        <v>0.225887445965806</v>
+        <v>0.2260000886252855</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4203797300336727</v>
+        <v>0.4156026876469264</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3013853629199288</v>
+        <v>0.3032853629199288</v>
       </c>
       <c r="C90">
-        <v>-271.5346203973868</v>
+        <v>-278.7685055092556</v>
       </c>
       <c r="D90">
-        <v>221.3269796026131</v>
+        <v>219.6937944907443</v>
       </c>
       <c r="E90">
-        <v>490.5916</v>
+        <v>496.1923</v>
       </c>
       <c r="F90">
-        <v>492.8616</v>
+        <v>498.4623</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8667,37 +8667,37 @@
         <v>48.3</v>
       </c>
       <c r="M90">
-        <v>116.21676528</v>
+        <v>117.53741034</v>
       </c>
       <c r="N90">
-        <v>-67.91676527999999</v>
+        <v>-69.23741034</v>
       </c>
       <c r="O90">
-        <v>-6.791676528</v>
+        <v>-6.923741034</v>
       </c>
       <c r="P90">
-        <v>-61.125088752</v>
+        <v>-62.31366930599999</v>
       </c>
       <c r="Q90">
-        <v>-51.42508875199999</v>
+        <v>-52.61366930599999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8542107077473133</v>
+        <v>0.9277025902697964</v>
       </c>
       <c r="T90">
-        <v>4.944139253800854</v>
+        <v>5.393606458691841</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04156026876469265</v>
+        <v>0.0410932994527298</v>
       </c>
       <c r="W90">
-        <v>0.2260000886252855</v>
+        <v>0.2261101999890463</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4156026876469264</v>
+        <v>0.410932994527298</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3032853629199288</v>
+        <v>0.3051853629199288</v>
       </c>
       <c r="C91">
-        <v>-278.7685055092556</v>
+        <v>-285.9784644313223</v>
       </c>
       <c r="D91">
-        <v>219.6937944907443</v>
+        <v>218.0845355686776</v>
       </c>
       <c r="E91">
-        <v>496.1923</v>
+        <v>501.7929999999999</v>
       </c>
       <c r="F91">
-        <v>498.4623</v>
+        <v>504.0629999999999</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8749,37 +8749,37 @@
         <v>48.3</v>
       </c>
       <c r="M91">
-        <v>117.53741034</v>
+        <v>118.8580554</v>
       </c>
       <c r="N91">
-        <v>-69.23741034</v>
+        <v>-70.55805539999999</v>
       </c>
       <c r="O91">
-        <v>-6.923741034</v>
+        <v>-7.055805539999999</v>
       </c>
       <c r="P91">
-        <v>-62.31366930599999</v>
+        <v>-63.50224985999998</v>
       </c>
       <c r="Q91">
-        <v>-52.61366930599999</v>
+        <v>-53.80224985999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9277025902697964</v>
+        <v>1.015892849296776</v>
       </c>
       <c r="T91">
-        <v>5.393606458691841</v>
+        <v>5.932967104561025</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0410932994527298</v>
+        <v>0.04063670723658836</v>
       </c>
       <c r="W91">
-        <v>0.2261101999890463</v>
+        <v>0.2262178644336125</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.410932994527298</v>
+        <v>0.4063670723658837</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3051853629199288</v>
+        <v>0.3070853629199288</v>
       </c>
       <c r="C92">
-        <v>-285.9784644313223</v>
+        <v>-293.1650191188942</v>
       </c>
       <c r="D92">
-        <v>218.0845355686776</v>
+        <v>216.4986808811057</v>
       </c>
       <c r="E92">
-        <v>501.7929999999999</v>
+        <v>507.3937</v>
       </c>
       <c r="F92">
-        <v>504.0629999999999</v>
+        <v>509.6636999999999</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8831,37 +8831,37 @@
         <v>48.3</v>
       </c>
       <c r="M92">
-        <v>118.8580554</v>
+        <v>120.17870046</v>
       </c>
       <c r="N92">
-        <v>-70.55805539999999</v>
+        <v>-71.87870045999999</v>
       </c>
       <c r="O92">
-        <v>-7.055805539999999</v>
+        <v>-7.187870046</v>
       </c>
       <c r="P92">
-        <v>-63.50224985999998</v>
+        <v>-64.69083041399999</v>
       </c>
       <c r="Q92">
-        <v>-53.80224985999998</v>
+        <v>-54.99083041399999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.015892849296776</v>
+        <v>1.123680943663085</v>
       </c>
       <c r="T92">
-        <v>5.932967104561025</v>
+        <v>6.592185671734473</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04063670723658836</v>
+        <v>0.04019015001420827</v>
       </c>
       <c r="W92">
-        <v>0.2262178644336125</v>
+        <v>0.2263231626266497</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4063670723658837</v>
+        <v>0.4019015001420827</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3070853629199288</v>
+        <v>0.3089853629199288</v>
       </c>
       <c r="C93">
-        <v>-293.1650191188942</v>
+        <v>-300.3286764547825</v>
       </c>
       <c r="D93">
-        <v>216.4986808811057</v>
+        <v>214.9357235452175</v>
       </c>
       <c r="E93">
-        <v>507.3937</v>
+        <v>512.9943999999999</v>
       </c>
       <c r="F93">
-        <v>509.6636999999999</v>
+        <v>515.2643999999999</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8913,37 +8913,37 @@
         <v>48.3</v>
       </c>
       <c r="M93">
-        <v>120.17870046</v>
+        <v>121.49934552</v>
       </c>
       <c r="N93">
-        <v>-71.87870045999999</v>
+        <v>-73.19934551999998</v>
       </c>
       <c r="O93">
-        <v>-7.187870046</v>
+        <v>-7.319934551999999</v>
       </c>
       <c r="P93">
-        <v>-64.69083041399999</v>
+        <v>-65.87941096799999</v>
       </c>
       <c r="Q93">
-        <v>-54.99083041399999</v>
+        <v>-56.17941096799998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.123680943663085</v>
+        <v>1.258416061620971</v>
       </c>
       <c r="T93">
-        <v>6.592185671734473</v>
+        <v>7.416208880701284</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04019015001420827</v>
+        <v>0.0397533005575321</v>
       </c>
       <c r="W93">
-        <v>0.2263231626266497</v>
+        <v>0.2264261717285339</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4019015001420827</v>
+        <v>0.3975330055753209</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3089853629199288</v>
+        <v>0.3108853629199288</v>
       </c>
       <c r="C94">
-        <v>-300.3286764547825</v>
+        <v>-307.4699287894629</v>
       </c>
       <c r="D94">
-        <v>214.9357235452175</v>
+        <v>213.3951712105371</v>
       </c>
       <c r="E94">
-        <v>512.9943999999999</v>
+        <v>518.5951</v>
       </c>
       <c r="F94">
-        <v>515.2643999999999</v>
+        <v>520.8651</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8995,37 +8995,37 @@
         <v>48.3</v>
       </c>
       <c r="M94">
-        <v>121.49934552</v>
+        <v>122.81999058</v>
       </c>
       <c r="N94">
-        <v>-73.19934551999998</v>
+        <v>-74.51999058</v>
       </c>
       <c r="O94">
-        <v>-7.319934551999999</v>
+        <v>-7.451999058</v>
       </c>
       <c r="P94">
-        <v>-65.87941096799999</v>
+        <v>-67.067991522</v>
       </c>
       <c r="Q94">
-        <v>-56.17941096799998</v>
+        <v>-57.367991522</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.258416061620971</v>
+        <v>1.431646927566824</v>
       </c>
       <c r="T94">
-        <v>7.416208880701284</v>
+        <v>8.475667292230039</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0397533005575321</v>
+        <v>0.03932584571282745</v>
       </c>
       <c r="W94">
-        <v>0.2264261717285339</v>
+        <v>0.2265269655809153</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3975330055753209</v>
+        <v>0.3932584571282745</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3108853629199288</v>
+        <v>0.3127853629199288</v>
       </c>
       <c r="C95">
-        <v>-307.4699287894629</v>
+        <v>-314.5892544581727</v>
       </c>
       <c r="D95">
-        <v>213.3951712105371</v>
+        <v>211.8765455418272</v>
       </c>
       <c r="E95">
-        <v>518.5951</v>
+        <v>524.1958</v>
       </c>
       <c r="F95">
-        <v>520.8651</v>
+        <v>526.4657999999999</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9077,37 +9077,37 @@
         <v>48.3</v>
       </c>
       <c r="M95">
-        <v>122.81999058</v>
+        <v>124.14063564</v>
       </c>
       <c r="N95">
-        <v>-74.51999058</v>
+        <v>-75.84063563999999</v>
       </c>
       <c r="O95">
-        <v>-7.451999058</v>
+        <v>-7.584063563999999</v>
       </c>
       <c r="P95">
-        <v>-67.067991522</v>
+        <v>-68.25657207599998</v>
       </c>
       <c r="Q95">
-        <v>-57.367991522</v>
+        <v>-58.55657207599998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.431646927566824</v>
+        <v>1.662621415494628</v>
       </c>
       <c r="T95">
-        <v>8.475667292230039</v>
+        <v>9.888278507601715</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03932584571282745</v>
+        <v>0.03890748565205269</v>
       </c>
       <c r="W95">
-        <v>0.2265269655809153</v>
+        <v>0.226625614883246</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3932584571282745</v>
+        <v>0.3890748565205269</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3127853629199288</v>
+        <v>0.3146853629199289</v>
       </c>
       <c r="C96">
-        <v>-314.5892544581727</v>
+        <v>-321.6871182760834</v>
       </c>
       <c r="D96">
-        <v>211.8765455418272</v>
+        <v>210.3793817239166</v>
       </c>
       <c r="E96">
-        <v>524.1958</v>
+        <v>529.7965</v>
       </c>
       <c r="F96">
-        <v>526.4657999999999</v>
+        <v>532.0665</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9159,37 +9159,37 @@
         <v>48.3</v>
       </c>
       <c r="M96">
-        <v>124.14063564</v>
+        <v>125.4612807</v>
       </c>
       <c r="N96">
-        <v>-75.84063563999999</v>
+        <v>-77.16128070000001</v>
       </c>
       <c r="O96">
-        <v>-7.584063563999999</v>
+        <v>-7.716128070000001</v>
       </c>
       <c r="P96">
-        <v>-68.25657207599998</v>
+        <v>-69.44515263000001</v>
       </c>
       <c r="Q96">
-        <v>-58.55657207599998</v>
+        <v>-59.74515263000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.662621415494628</v>
+        <v>1.985985698593555</v>
       </c>
       <c r="T96">
-        <v>9.888278507601715</v>
+        <v>11.86593420912207</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03890748565205269</v>
+        <v>0.03849793317150476</v>
       </c>
       <c r="W96">
-        <v>0.226625614883246</v>
+        <v>0.2267221873581592</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3890748565205269</v>
+        <v>0.3849793317150476</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3146853629199289</v>
+        <v>0.3165853629199288</v>
       </c>
       <c r="C97">
-        <v>-321.6871182760834</v>
+        <v>-328.7639720126265</v>
       </c>
       <c r="D97">
-        <v>210.3793817239166</v>
+        <v>208.9032279873735</v>
       </c>
       <c r="E97">
-        <v>529.7965</v>
+        <v>535.3972</v>
       </c>
       <c r="F97">
-        <v>532.0665</v>
+        <v>537.6672</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9241,37 +9241,37 @@
         <v>48.3</v>
       </c>
       <c r="M97">
-        <v>125.4612807</v>
+        <v>126.78192576</v>
       </c>
       <c r="N97">
-        <v>-77.16128070000001</v>
+        <v>-78.48192576000001</v>
       </c>
       <c r="O97">
-        <v>-7.716128070000001</v>
+        <v>-7.848192576000002</v>
       </c>
       <c r="P97">
-        <v>-69.44515263000001</v>
+        <v>-70.63373318400001</v>
       </c>
       <c r="Q97">
-        <v>-59.74515263000001</v>
+        <v>-60.933733184</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.985985698593555</v>
+        <v>2.471032123241944</v>
       </c>
       <c r="T97">
-        <v>11.86593420912207</v>
+        <v>14.83241776140259</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03849793317150476</v>
+        <v>0.03809691303430159</v>
       </c>
       <c r="W97">
-        <v>0.2267221873581592</v>
+        <v>0.2268167479065117</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3849793317150476</v>
+        <v>0.3809691303430158</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3165853629199288</v>
+        <v>0.3184853629199288</v>
       </c>
       <c r="C98">
-        <v>-328.7639720126264</v>
+        <v>-335.8202548459909</v>
       </c>
       <c r="D98">
-        <v>208.9032279873735</v>
+        <v>207.4476451540091</v>
       </c>
       <c r="E98">
-        <v>535.3971999999999</v>
+        <v>540.9979</v>
       </c>
       <c r="F98">
-        <v>537.6671999999999</v>
+        <v>543.2678999999999</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9323,37 +9323,37 @@
         <v>48.3</v>
       </c>
       <c r="M98">
-        <v>126.78192576</v>
+        <v>128.10257082</v>
       </c>
       <c r="N98">
-        <v>-78.48192575999998</v>
+        <v>-79.80257081999999</v>
       </c>
       <c r="O98">
-        <v>-7.848192575999999</v>
+        <v>-7.980257081999999</v>
       </c>
       <c r="P98">
-        <v>-70.63373318399998</v>
+        <v>-71.82231373799999</v>
       </c>
       <c r="Q98">
-        <v>-60.93373318399998</v>
+        <v>-62.12231373799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.471032123241938</v>
+        <v>3.27944283098925</v>
       </c>
       <c r="T98">
-        <v>14.83241776140255</v>
+        <v>19.7765570152034</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03809691303430159</v>
+        <v>0.0377041613535356</v>
       </c>
       <c r="W98">
-        <v>0.2268167479065117</v>
+        <v>0.2269093587528363</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3809691303430159</v>
+        <v>0.3770416135353559</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3184853629199288</v>
+        <v>0.3203853629199288</v>
       </c>
       <c r="C99">
-        <v>-335.8202548459909</v>
+        <v>-342.8563937987495</v>
       </c>
       <c r="D99">
-        <v>207.4476451540091</v>
+        <v>206.0122062012504</v>
       </c>
       <c r="E99">
-        <v>540.9979</v>
+        <v>546.5985999999999</v>
       </c>
       <c r="F99">
-        <v>543.2678999999999</v>
+        <v>548.8685999999999</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9405,37 +9405,37 @@
         <v>48.3</v>
       </c>
       <c r="M99">
-        <v>128.10257082</v>
+        <v>129.42321588</v>
       </c>
       <c r="N99">
-        <v>-79.80257081999999</v>
+        <v>-81.12321587999999</v>
       </c>
       <c r="O99">
-        <v>-7.980257081999999</v>
+        <v>-8.112321587999999</v>
       </c>
       <c r="P99">
-        <v>-71.82231373799999</v>
+        <v>-73.01089429199999</v>
       </c>
       <c r="Q99">
-        <v>-62.12231373799999</v>
+        <v>-63.31089429199999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.27944283098925</v>
+        <v>4.896264246483875</v>
       </c>
       <c r="T99">
-        <v>19.7765570152034</v>
+        <v>29.6648355228051</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0377041613535356</v>
+        <v>0.03731942501319339</v>
       </c>
       <c r="W99">
-        <v>0.2269093587528363</v>
+        <v>0.227000079581889</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3770416135353559</v>
+        <v>0.373194250131934</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3203853629199288</v>
+        <v>0.3222853629199288</v>
       </c>
       <c r="C100">
-        <v>-342.8563937987495</v>
+        <v>-349.8728041555243</v>
       </c>
       <c r="D100">
-        <v>206.0122062012504</v>
+        <v>204.5964958444757</v>
       </c>
       <c r="E100">
-        <v>546.5985999999999</v>
+        <v>552.1993</v>
       </c>
       <c r="F100">
-        <v>548.8685999999999</v>
+        <v>554.4693</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9487,37 +9487,37 @@
         <v>48.3</v>
       </c>
       <c r="M100">
-        <v>129.42321588</v>
+        <v>130.74386094</v>
       </c>
       <c r="N100">
-        <v>-81.12321587999999</v>
+        <v>-82.44386093999999</v>
       </c>
       <c r="O100">
-        <v>-8.112321587999999</v>
+        <v>-8.244386093999999</v>
       </c>
       <c r="P100">
-        <v>-73.01089429199999</v>
+        <v>-74.19947484599999</v>
       </c>
       <c r="Q100">
-        <v>-63.31089429199999</v>
+        <v>-64.49947484599998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.896264246483875</v>
+        <v>9.746728492967751</v>
       </c>
       <c r="T100">
-        <v>29.6648355228051</v>
+        <v>59.32967104561019</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03731942501319339</v>
+        <v>0.03694246112417123</v>
       </c>
       <c r="W100">
-        <v>0.227000079581889</v>
+        <v>0.2270889676669204</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.373194250131934</v>
+        <v>0.3694246112417123</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3222853629199288</v>
-      </c>
-      <c r="C101">
-        <v>-349.8728041555243</v>
-      </c>
-      <c r="D101">
-        <v>204.5964958444757</v>
-      </c>
-      <c r="E101">
-        <v>552.1993</v>
-      </c>
-      <c r="F101">
-        <v>554.4693</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>557.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>58</v>
-      </c>
-      <c r="K101">
-        <v>9.700000000000003</v>
-      </c>
-      <c r="L101">
-        <v>48.3</v>
-      </c>
-      <c r="M101">
-        <v>130.74386094</v>
-      </c>
-      <c r="N101">
-        <v>-82.44386093999999</v>
-      </c>
-      <c r="O101">
-        <v>-8.244386093999999</v>
-      </c>
-      <c r="P101">
-        <v>-74.19947484599999</v>
-      </c>
-      <c r="Q101">
-        <v>-64.49947484599998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.746728492967751</v>
-      </c>
-      <c r="T101">
-        <v>59.32967104561019</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03694246112417123</v>
-      </c>
-      <c r="W101">
-        <v>0.2270889676669204</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3694246112417123</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
